--- a/UK-tech-data.xlsx
+++ b/UK-tech-data.xlsx
@@ -5673,7 +5673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5691,7 +5691,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Verified unicorns &amp; $1B exits headquartered in each UK city.</t>
+          <t>Verified unicorns &amp; $1B exits, founded-or-HQ basis, by UK city. (UK-founded unicorns now HQ'd abroad have no UK city and sit in the national total.)</t>
         </is>
       </c>
     </row>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Oxford</t>
         </is>
       </c>
       <c r="C7" s="12" t="n">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Oxford</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="C8" s="12" t="n">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Reigate</t>
+          <t>Milton</t>
         </is>
       </c>
       <c r="C9" s="12" t="n">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bristol</t>
+          <t>Reigate</t>
         </is>
       </c>
       <c r="C10" s="12" t="n">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sheffield</t>
+          <t>Leeds</t>
         </is>
       </c>
       <c r="C11" s="12" t="n">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Milton</t>
+          <t>Nottingham</t>
         </is>
       </c>
       <c r="C12" s="12" t="n">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Sheffield</t>
         </is>
       </c>
       <c r="C13" s="12" t="n">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nottingham</t>
+          <t>Bristol</t>
         </is>
       </c>
       <c r="C14" s="12" t="n">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hatfield</t>
+          <t>Babraham</t>
         </is>
       </c>
       <c r="C15" s="12" t="n">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Babraham</t>
+          <t>Horsham</t>
         </is>
       </c>
       <c r="C16" s="12" t="n">
@@ -5874,36 +5874,10 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Horsham</t>
+          <t>Crewe</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Crewe</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Cheltenham</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="n">
         <v>1</v>
       </c>
     </row>

--- a/UK-tech-data.xlsx
+++ b/UK-tech-data.xlsx
@@ -14,7 +14,7 @@
     <sheet name="AI VC quarterly" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Shares" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Unicorns by country" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="UK unicorn cities" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="UK unicorn metros" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="UK cities by VC" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="UK cities by AI VC" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
@@ -657,7 +657,7 @@
     <row r="23">
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>•  Even excluding London, the rest of the UK (76 unicorns) would out-rank France, Sweden and Australia.</t>
+          <t>•  Excluding the London metro, the rest of the UK (64 unicorns) ranks ahead of Sweden and Australia.</t>
         </is>
       </c>
     </row>
@@ -5611,29 +5611,29 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="n">
+      <c r="A12" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>United Kingdom (ex-London)</t>
         </is>
       </c>
-      <c r="C12" s="14" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="n">
-        <v>66</v>
+      <c r="C13" s="14" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -5673,7 +5673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5684,14 +5684,14 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>UK cities by number of unicorns</t>
+          <t>UK metro areas by number of unicorns</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Verified unicorns &amp; $1B exits, founded-or-HQ basis, by UK city. (UK-founded unicorns now HQ'd abroad have no UK city and sit in the national total.)</t>
+          <t>Verified unicorns &amp; $1B exits, founded-or-HQ basis, by UK metro area (satellite towns rolled into their metro).</t>
         </is>
       </c>
     </row>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -5722,7 +5722,7 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>143</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6">
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -5744,11 +5744,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Oxford</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -5757,11 +5757,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Oxford</t>
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Milton</t>
+          <t>Nottingham</t>
         </is>
       </c>
       <c r="C9" s="12" t="n">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Reigate</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="C10" s="12" t="n">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Bristol</t>
         </is>
       </c>
       <c r="C11" s="12" t="n">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nottingham</t>
+          <t>Sheffield</t>
         </is>
       </c>
       <c r="C12" s="12" t="n">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sheffield</t>
+          <t>Leeds–Bradford</t>
         </is>
       </c>
       <c r="C13" s="12" t="n">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bristol</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="C14" s="12" t="n">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Babraham</t>
+          <t>Windsor-Maidenhead</t>
         </is>
       </c>
       <c r="C15" s="12" t="n">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Horsham</t>
+          <t>Newcastle upon Tyne</t>
         </is>
       </c>
       <c r="C16" s="12" t="n">
@@ -5874,10 +5874,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Crewe</t>
+          <t>Glasgow</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Cardiff-Newport</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="n">
         <v>1</v>
       </c>
     </row>

--- a/UK-tech-data.xlsx
+++ b/UK-tech-data.xlsx
@@ -15,8 +15,8 @@
     <sheet name="Shares" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Unicorns by country" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="UK unicorn metros" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="UK cities by VC" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="UK cities by AI VC" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="UK metros by VC" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="UK metros by AI VC" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -694,21 +694,21 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>UK cities by AI VC funding (annual)</t>
+          <t>UK metro areas by AI VC funding (annual)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Top cities by AI VC raised, $B per year.</t>
+          <t>Top metro areas by AI VC raised, $B per year.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="10" t="n">
-        <v>2.89</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="10" t="n">
-        <v>2.32</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="10" t="n">
-        <v>0.63</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="10">
@@ -1032,7 +1032,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Altrincham</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
@@ -1072,13 +1072,13 @@
         <v>0</v>
       </c>
       <c r="N11" s="10" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Glasgow</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
@@ -1118,13 +1118,13 @@
         <v>0</v>
       </c>
       <c r="N12" s="10" t="n">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Wallingford</t>
+          <t>Leeds–Bradford</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
@@ -1164,13 +1164,13 @@
         <v>0</v>
       </c>
       <c r="N13" s="10" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Milton</t>
+          <t>Belfast</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
@@ -1210,13 +1210,13 @@
         <v>0</v>
       </c>
       <c r="N14" s="10" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Glasgow</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
@@ -1256,13 +1256,13 @@
         <v>0</v>
       </c>
       <c r="N15" s="10" t="n">
-        <v>0.16</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Milton Keynes</t>
+          <t>Cardiff-Newport</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="10" t="n">
-        <v>0.15</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -5927,21 +5927,21 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>UK cities by VC funding (annual)</t>
+          <t>UK metro areas by VC funding (annual)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Top cities by total VC raised, $B per year.</t>
+          <t>Top metro areas by total VC raised, $B per year.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="B4" s="7" t="n">
@@ -6075,7 +6075,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="10" t="n">
-        <v>10.19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -6121,7 +6121,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="10" t="n">
-        <v>5.45</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -6167,7 +6167,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="10" t="n">
-        <v>3.12</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="9">
@@ -6213,7 +6213,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="10" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="10">
@@ -6259,13 +6259,13 @@
         <v>0</v>
       </c>
       <c r="N10" s="10" t="n">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Milton</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
@@ -6305,13 +6305,13 @@
         <v>0</v>
       </c>
       <c r="N11" s="10" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Glasgow</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
@@ -6351,13 +6351,13 @@
         <v>0</v>
       </c>
       <c r="N12" s="10" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Loughborough</t>
+          <t>Leeds–Bradford</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
@@ -6397,13 +6397,13 @@
         <v>0</v>
       </c>
       <c r="N13" s="10" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
@@ -6443,13 +6443,13 @@
         <v>0</v>
       </c>
       <c r="N14" s="10" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Newcastle upon Tyne</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
@@ -6489,13 +6489,13 @@
         <v>0</v>
       </c>
       <c r="N15" s="10" t="n">
-        <v>1.03</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Billingham</t>
+          <t>Cardiff-Newport</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
@@ -6535,7 +6535,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="10" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
     </row>
   </sheetData>

--- a/UK-tech-data.xlsx
+++ b/UK-tech-data.xlsx
@@ -17,6 +17,7 @@
     <sheet name="UK unicorn metros" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="UK metros by VC" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="UK metros by AI VC" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Top rounds" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +29,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,6 +58,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000B1F3A"/>
+      <sz val="13"/>
     </font>
   </fonts>
   <fills count="5">
@@ -94,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -116,6 +122,7 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1310,6 +1317,676 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Largest UK VC rounds</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Top 10 VC rounds by deal size, 2025 and 2026 year-to-date (to 25 June 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Amount ($m)</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Round</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Lead investors</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Revolut</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Late VC</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>07/2025</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mubadala Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Nscale</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Series B</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>09/2025</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Aker ASA, G Squared, Nvidia</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Kraken</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Early VC</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>D1 Capital Partners, Ontario Teachers’ Pension Plan, Durable Capital Partners</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>CityFibre</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>660</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Growth Equity VC</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>07/2025</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Antin Infrastructure Partners, Mubadala Capital, Interogo Holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>FNZ</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>650</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Growth Equity VC</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>11/2025</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ninety One, Nucleus Financial, Aberdeen</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Quantinuum</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>600</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Late VC</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>09/2025</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Quanta Computer, NVentures, QED Investors</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Isomorphic Labs</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>600</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Late VC</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>03/2025</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Thrive Capital, GV</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Rapyd</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>500</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Series F</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>03/2025</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>XBO.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>FNZ</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>500</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Growth Equity VC</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>04/2025</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Nscale</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>433</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Late VC</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>10/2025</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Nvidia, Dell Technologies Capital, Blue Owl Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Amount ($m)</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Round</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Lead investors</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Isomorphic Labs</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>2100</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Series B</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>05/2026</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Thrive Capital, UK Sovereign AI, GV</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Nscale</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Series C</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>03/2026</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Aker ASA, 8090 Industries, Dell</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Wayve</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Series D</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>02/2026</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SoftBank Vision Fund, Eclipse Ventures, Balderton Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Ineffable Intelligence</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>04/2026</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Sequoia, Lightspeed Venture Partners, Government of the United Kingdom</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Recursive Superintelligence</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>650</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>05/2026</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>GV, Nvidia, Greycroft Partners</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>ElevenLabs</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>500</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Series D</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>02/2026</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Sequoia, Smash Capital, ICONIQ Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>7</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>CuspAI</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>400</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Late VC</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>06/2026</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Kleiner Perkins, Bezos Expeditions</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>8</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Oxford Quantum Circuits</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>350</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Series C</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>06/2026</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Bullhound Capital, Fynveur, Firgun Ventures</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>PhysicsX</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="n">
+        <v>300</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Series C</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>06/2026</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Temasek, Intrepid Growth Partners, July Fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>10</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Cambridge Aerospace</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>300</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Late VC</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>06/2026</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>DFJ Growth</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/UK-tech-data.xlsx
+++ b/UK-tech-data.xlsx
@@ -115,11 +115,11 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -609,7 +609,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>All funding values in US dollars, billions ($B).</t>
+          <t>US dollars. Funding in millions ($m) on the detail tabs; the Shares tab is in billions ($B). Top rounds in $m.</t>
         </is>
       </c>
     </row>
@@ -683,19 +683,19 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -708,7 +708,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Top metro areas by AI VC raised, $B per year.</t>
+          <t>Top metro areas by AI VC raised, $m per year.</t>
         </is>
       </c>
     </row>
@@ -767,43 +767,43 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>0</v>
+        <v>954</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>0</v>
+        <v>1213</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>0</v>
+        <v>2403</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>0</v>
+        <v>2398</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0</v>
+        <v>2885</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0</v>
+        <v>3771</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>0</v>
+        <v>2674</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>0</v>
+        <v>4352</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0</v>
+        <v>6987</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>0</v>
+        <v>11484</v>
       </c>
       <c r="N5" s="10" t="n">
-        <v>40.13</v>
+        <v>40133</v>
       </c>
     </row>
     <row r="6">
@@ -813,43 +813,43 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>0</v>
+        <v>259</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>0</v>
+        <v>1166</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0</v>
+        <v>271</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>0</v>
+        <v>282</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="N6" s="10" t="n">
-        <v>3.16</v>
+        <v>3164</v>
       </c>
     </row>
     <row r="7">
@@ -859,43 +859,43 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>0</v>
+        <v>262</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>0</v>
+        <v>259</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>0</v>
+        <v>516</v>
       </c>
       <c r="N7" s="10" t="n">
-        <v>2.51</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="8">
@@ -905,43 +905,43 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>0</v>
+        <v>379</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M8" s="8" t="n">
         <v>0</v>
       </c>
       <c r="N8" s="10" t="n">
-        <v>1.01</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="9">
@@ -951,43 +951,43 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>0</v>
+        <v>379</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="N9" s="10" t="n">
-        <v>0.99</v>
+        <v>995</v>
       </c>
     </row>
     <row r="10">
@@ -997,43 +997,43 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="N10" s="10" t="n">
-        <v>0.35</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -1046,40 +1046,40 @@
         <v>0</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N11" s="10" t="n">
-        <v>0.35</v>
+        <v>348</v>
       </c>
     </row>
     <row r="12">
@@ -1089,43 +1089,43 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="N12" s="10" t="n">
-        <v>0.22</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13">
@@ -1135,43 +1135,43 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="N13" s="10" t="n">
-        <v>0.17</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14">
@@ -1184,40 +1184,40 @@
         <v>0</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N14" s="10" t="n">
-        <v>0.15</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15">
@@ -1227,43 +1227,43 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" s="8" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N15" s="10" t="n">
-        <v>0.07000000000000001</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16">
@@ -1279,37 +1279,37 @@
         <v>0</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N16" s="10" t="n">
-        <v>0.07000000000000001</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1323,15 +1323,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="56" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1373,15 +1372,10 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Round</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Lead investors</t>
         </is>
@@ -1396,20 +1390,15 @@
           <t>Revolut</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="8" t="n">
         <v>2000</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Late VC</t>
+          <t>07/2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
-        <is>
-          <t>07/2025</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
         <is>
           <t>Mubadala Capital</t>
         </is>
@@ -1424,20 +1413,15 @@
           <t>Nscale</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="8" t="n">
         <v>1100</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>09/2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
-        <is>
-          <t>09/2025</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
         <is>
           <t>Aker ASA, G Squared, Nvidia</t>
         </is>
@@ -1452,20 +1436,15 @@
           <t>Kraken</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="8" t="n">
         <v>1000</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Early VC</t>
+          <t>12/2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
-        <is>
-          <t>12/2025</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
         <is>
           <t>D1 Capital Partners, Ontario Teachers’ Pension Plan, Durable Capital Partners</t>
         </is>
@@ -1480,20 +1459,15 @@
           <t>CityFibre</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="8" t="n">
         <v>660</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Growth Equity VC</t>
+          <t>07/2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
-        <is>
-          <t>07/2025</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
         <is>
           <t>Antin Infrastructure Partners, Mubadala Capital, Interogo Holding</t>
         </is>
@@ -1508,20 +1482,15 @@
           <t>FNZ</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="8" t="n">
         <v>650</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Growth Equity VC</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
-        <is>
-          <t>11/2025</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
         <is>
           <t>Ninety One, Nucleus Financial, Aberdeen</t>
         </is>
@@ -1536,20 +1505,15 @@
           <t>Quantinuum</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="8" t="n">
         <v>600</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Late VC</t>
+          <t>09/2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
-        <is>
-          <t>09/2025</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
         <is>
           <t>Quanta Computer, NVentures, QED Investors</t>
         </is>
@@ -1564,20 +1528,15 @@
           <t>Isomorphic Labs</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="8" t="n">
         <v>600</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Late VC</t>
+          <t>03/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
-        <is>
-          <t>03/2025</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
         <is>
           <t>Thrive Capital, GV</t>
         </is>
@@ -1592,20 +1551,15 @@
           <t>Rapyd</t>
         </is>
       </c>
-      <c r="C13" s="12" t="n">
+      <c r="C13" s="8" t="n">
         <v>500</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Series F</t>
+          <t>03/2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>03/2025</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
         <is>
           <t>XBO.com</t>
         </is>
@@ -1620,20 +1574,15 @@
           <t>FNZ</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="C14" s="8" t="n">
         <v>500</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Growth Equity VC</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
           <t>04/2025</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1644,20 +1593,15 @@
           <t>Nscale</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="C15" s="8" t="n">
         <v>433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Late VC</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>10/2025</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
         <is>
           <t>Nvidia, Dell Technologies Capital, Blue Owl Capital</t>
         </is>
@@ -1688,15 +1632,10 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Round</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>Lead investors</t>
         </is>
@@ -1711,20 +1650,15 @@
           <t>Isomorphic Labs</t>
         </is>
       </c>
-      <c r="C19" s="12" t="n">
+      <c r="C19" s="8" t="n">
         <v>2100</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Series B</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
-        <is>
-          <t>05/2026</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
         <is>
           <t>Thrive Capital, UK Sovereign AI, GV</t>
         </is>
@@ -1739,20 +1673,15 @@
           <t>Nscale</t>
         </is>
       </c>
-      <c r="C20" s="12" t="n">
+      <c r="C20" s="8" t="n">
         <v>2000</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Series C</t>
+          <t>03/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
-        <is>
-          <t>03/2026</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
         <is>
           <t>Aker ASA, 8090 Industries, Dell</t>
         </is>
@@ -1767,20 +1696,15 @@
           <t>Wayve</t>
         </is>
       </c>
-      <c r="C21" s="12" t="n">
+      <c r="C21" s="8" t="n">
         <v>1200</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Series D</t>
+          <t>02/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>02/2026</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
         <is>
           <t>SoftBank Vision Fund, Eclipse Ventures, Balderton Capital</t>
         </is>
@@ -1795,20 +1719,15 @@
           <t>Ineffable Intelligence</t>
         </is>
       </c>
-      <c r="C22" s="12" t="n">
+      <c r="C22" s="8" t="n">
         <v>1100</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Seed</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
-        <is>
-          <t>04/2026</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
         <is>
           <t>Sequoia, Lightspeed Venture Partners, Government of the United Kingdom</t>
         </is>
@@ -1823,20 +1742,15 @@
           <t>Recursive Superintelligence</t>
         </is>
       </c>
-      <c r="C23" s="12" t="n">
+      <c r="C23" s="8" t="n">
         <v>650</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Seed</t>
+          <t>05/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>05/2026</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
         <is>
           <t>GV, Nvidia, Greycroft Partners</t>
         </is>
@@ -1851,20 +1765,15 @@
           <t>ElevenLabs</t>
         </is>
       </c>
-      <c r="C24" s="12" t="n">
+      <c r="C24" s="8" t="n">
         <v>500</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Series D</t>
+          <t>02/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
-        <is>
-          <t>02/2026</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
         <is>
           <t>Sequoia, Smash Capital, ICONIQ Capital</t>
         </is>
@@ -1879,20 +1788,15 @@
           <t>CuspAI</t>
         </is>
       </c>
-      <c r="C25" s="12" t="n">
+      <c r="C25" s="8" t="n">
         <v>400</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Late VC</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
-        <is>
-          <t>06/2026</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
         <is>
           <t>Kleiner Perkins, Bezos Expeditions</t>
         </is>
@@ -1907,20 +1811,15 @@
           <t>Oxford Quantum Circuits</t>
         </is>
       </c>
-      <c r="C26" s="12" t="n">
+      <c r="C26" s="8" t="n">
         <v>350</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Series C</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
-        <is>
-          <t>06/2026</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
         <is>
           <t>Bullhound Capital, Fynveur, Firgun Ventures</t>
         </is>
@@ -1935,20 +1834,15 @@
           <t>PhysicsX</t>
         </is>
       </c>
-      <c r="C27" s="12" t="n">
+      <c r="C27" s="8" t="n">
         <v>300</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Series C</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
-        <is>
-          <t>06/2026</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
         <is>
           <t>Temasek, Intrepid Growth Partners, July Fund</t>
         </is>
@@ -1963,20 +1857,15 @@
           <t>Cambridge Aerospace</t>
         </is>
       </c>
-      <c r="C28" s="12" t="n">
+      <c r="C28" s="8" t="n">
         <v>300</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Late VC</t>
+          <t>06/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
-        <is>
-          <t>06/2026</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
         <is>
           <t>DFJ Growth</t>
         </is>
@@ -1997,18 +1886,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2021,7 +1910,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>By stage (round-size band), $B. 2026 = year-to-date.</t>
+          <t>By stage (round-size band), $m. 2026 = to 25 June 2026.</t>
         </is>
       </c>
     </row>
@@ -2099,40 +1988,40 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>0.312</v>
+        <v>312</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>0.329</v>
+        <v>329</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>0.324</v>
+        <v>324</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>0.381</v>
+        <v>381</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>0.35</v>
+        <v>350</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>0.386</v>
+        <v>386</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0.476</v>
+        <v>476</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.385</v>
+        <v>385</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>0.281</v>
+        <v>281</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>0.2</v>
+        <v>200</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0.207</v>
+        <v>207</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>0.064</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6">
@@ -2142,40 +2031,40 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>0.89</v>
+        <v>890</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>0.999</v>
+        <v>999</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>1.201</v>
+        <v>1201</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>1.3</v>
+        <v>1300</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>1.341</v>
+        <v>1341</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>1.316</v>
+        <v>1316</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>2.009</v>
+        <v>2009</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>1.694</v>
+        <v>1694</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>1.354</v>
+        <v>1354</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>1.07</v>
+        <v>1070</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>1.15</v>
+        <v>1150</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>0.424</v>
+        <v>424</v>
       </c>
     </row>
     <row r="7">
@@ -2185,40 +2074,40 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1.253</v>
+        <v>1253</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>1.654</v>
+        <v>1654</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>2.225</v>
+        <v>2225</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>2.552</v>
+        <v>2552</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>2.834</v>
+        <v>2834</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>2.925</v>
+        <v>2925</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>4.127</v>
+        <v>4127</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>3.647</v>
+        <v>3647</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>3.212</v>
+        <v>3212</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>2.8</v>
+        <v>2800</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>2.882</v>
+        <v>2882</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>1.147</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="8">
@@ -2228,40 +2117,40 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>1.429</v>
+        <v>1429</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>1.859</v>
+        <v>1859</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>2.004</v>
+        <v>2004</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>2.61</v>
+        <v>2610</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>2.845</v>
+        <v>2845</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>3.004</v>
+        <v>3004</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>4.447</v>
+        <v>4447</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>4.963</v>
+        <v>4963</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>3.262</v>
+        <v>3262</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>3.429</v>
+        <v>3429</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>3.626</v>
+        <v>3626</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>1.817</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="9">
@@ -2271,40 +2160,40 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>1.344</v>
+        <v>1344</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>1.184</v>
+        <v>1184</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>1.855</v>
+        <v>1855</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>2.507</v>
+        <v>2507</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>2.57</v>
+        <v>2570</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>3.777</v>
+        <v>3777</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>7.074</v>
+        <v>7074</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>6.167</v>
+        <v>6167</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>3.975</v>
+        <v>3975</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>3.637</v>
+        <v>3637</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>3.831</v>
+        <v>3831</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>1.919</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="10">
@@ -2314,40 +2203,40 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.836</v>
+        <v>836</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>0.622</v>
+        <v>622</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>1.211</v>
+        <v>1211</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>1.767</v>
+        <v>1767</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>2.254</v>
+        <v>2254</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>3.477</v>
+        <v>3477</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>7.406</v>
+        <v>7406</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>7.903</v>
+        <v>7903</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>2.797</v>
+        <v>2797</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>2.968</v>
+        <v>2968</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>3.191</v>
+        <v>3191</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>2.787</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="11">
@@ -2357,40 +2246,40 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>1.433</v>
+        <v>1433</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>2.703</v>
+        <v>2703</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>1.901</v>
+        <v>1901</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>0.5</v>
+        <v>500</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>5.451</v>
+        <v>5451</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>2.578</v>
+        <v>2578</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>14.35</v>
+        <v>14350</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>6.007</v>
+        <v>6007</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>4.466</v>
+        <v>4466</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>4.468</v>
+        <v>4468</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>8.773999999999999</v>
+        <v>8774</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>8.9</v>
+        <v>8900</v>
       </c>
     </row>
     <row r="12">
@@ -2400,40 +2289,40 @@
         </is>
       </c>
       <c r="B12" s="10" t="n">
-        <v>7.497</v>
+        <v>7497</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>9.35</v>
+        <v>9350</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>10.72</v>
+        <v>10720</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>11.617</v>
+        <v>11617</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>17.645</v>
+        <v>17645</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>17.464</v>
+        <v>17464</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>39.89</v>
+        <v>39890</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>30.765</v>
+        <v>30765</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>19.347</v>
+        <v>19347</v>
       </c>
       <c r="K12" s="10" t="n">
-        <v>18.573</v>
+        <v>18573</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>23.661</v>
+        <v>23661</v>
       </c>
       <c r="M12" s="10" t="n">
-        <v>17.058</v>
+        <v>17058</v>
       </c>
     </row>
   </sheetData>
@@ -2451,52 +2340,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="10" customWidth="1" min="26" max="26"/>
-    <col width="10" customWidth="1" min="27" max="27"/>
-    <col width="10" customWidth="1" min="28" max="28"/>
-    <col width="10" customWidth="1" min="29" max="29"/>
-    <col width="10" customWidth="1" min="30" max="30"/>
-    <col width="10" customWidth="1" min="31" max="31"/>
-    <col width="10" customWidth="1" min="32" max="32"/>
-    <col width="10" customWidth="1" min="33" max="33"/>
-    <col width="10" customWidth="1" min="34" max="34"/>
-    <col width="10" customWidth="1" min="35" max="35"/>
-    <col width="10" customWidth="1" min="36" max="36"/>
-    <col width="10" customWidth="1" min="37" max="37"/>
-    <col width="10" customWidth="1" min="38" max="38"/>
-    <col width="10" customWidth="1" min="39" max="39"/>
-    <col width="10" customWidth="1" min="40" max="40"/>
-    <col width="10" customWidth="1" min="41" max="41"/>
-    <col width="10" customWidth="1" min="42" max="42"/>
-    <col width="10" customWidth="1" min="43" max="43"/>
-    <col width="10" customWidth="1" min="44" max="44"/>
-    <col width="10" customWidth="1" min="45" max="45"/>
-    <col width="10" customWidth="1" min="46" max="46"/>
-    <col width="10" customWidth="1" min="47" max="47"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="31" max="31"/>
+    <col width="11" customWidth="1" min="32" max="32"/>
+    <col width="11" customWidth="1" min="33" max="33"/>
+    <col width="11" customWidth="1" min="34" max="34"/>
+    <col width="11" customWidth="1" min="35" max="35"/>
+    <col width="11" customWidth="1" min="36" max="36"/>
+    <col width="11" customWidth="1" min="37" max="37"/>
+    <col width="11" customWidth="1" min="38" max="38"/>
+    <col width="11" customWidth="1" min="39" max="39"/>
+    <col width="11" customWidth="1" min="40" max="40"/>
+    <col width="11" customWidth="1" min="41" max="41"/>
+    <col width="11" customWidth="1" min="42" max="42"/>
+    <col width="11" customWidth="1" min="43" max="43"/>
+    <col width="11" customWidth="1" min="44" max="44"/>
+    <col width="11" customWidth="1" min="45" max="45"/>
+    <col width="11" customWidth="1" min="46" max="46"/>
+    <col width="11" customWidth="1" min="47" max="47"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2509,7 +2398,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>By stage (round-size band), $B.</t>
+          <t>By stage (round-size band), $m.</t>
         </is>
       </c>
     </row>
@@ -2757,142 +2646,142 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>0.089</v>
+        <v>89</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>0.074</v>
+        <v>74</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>0.081</v>
+        <v>81</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>0.067</v>
+        <v>67</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>0.091</v>
+        <v>91</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>0.076</v>
+        <v>76</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0.075</v>
+        <v>75</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.08699999999999999</v>
+        <v>87</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>0.082</v>
+        <v>82</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>0.08599999999999999</v>
+        <v>86</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0.075</v>
+        <v>75</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>0.081</v>
+        <v>81</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>0.097</v>
+        <v>97</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>0.103</v>
+        <v>103</v>
       </c>
       <c r="P5" s="8" t="n">
-        <v>0.083</v>
+        <v>83</v>
       </c>
       <c r="Q5" s="8" t="n">
-        <v>0.098</v>
+        <v>98</v>
       </c>
       <c r="R5" s="8" t="n">
-        <v>0.08699999999999999</v>
+        <v>87</v>
       </c>
       <c r="S5" s="8" t="n">
-        <v>0.098</v>
+        <v>98</v>
       </c>
       <c r="T5" s="8" t="n">
-        <v>0.081</v>
+        <v>81</v>
       </c>
       <c r="U5" s="8" t="n">
-        <v>0.082</v>
+        <v>82</v>
       </c>
       <c r="V5" s="8" t="n">
-        <v>0.106</v>
+        <v>106</v>
       </c>
       <c r="W5" s="8" t="n">
-        <v>0.1</v>
+        <v>100</v>
       </c>
       <c r="X5" s="8" t="n">
-        <v>0.078</v>
+        <v>78</v>
       </c>
       <c r="Y5" s="8" t="n">
-        <v>0.102</v>
+        <v>102</v>
       </c>
       <c r="Z5" s="8" t="n">
-        <v>0.131</v>
+        <v>131</v>
       </c>
       <c r="AA5" s="8" t="n">
-        <v>0.118</v>
+        <v>118</v>
       </c>
       <c r="AB5" s="8" t="n">
-        <v>0.109</v>
+        <v>109</v>
       </c>
       <c r="AC5" s="8" t="n">
-        <v>0.118</v>
+        <v>118</v>
       </c>
       <c r="AD5" s="8" t="n">
-        <v>0.117</v>
+        <v>117</v>
       </c>
       <c r="AE5" s="8" t="n">
-        <v>0.111</v>
+        <v>111</v>
       </c>
       <c r="AF5" s="8" t="n">
-        <v>0.07099999999999999</v>
+        <v>71</v>
       </c>
       <c r="AG5" s="8" t="n">
-        <v>0.08599999999999999</v>
+        <v>86</v>
       </c>
       <c r="AH5" s="8" t="n">
-        <v>0.074</v>
+        <v>74</v>
       </c>
       <c r="AI5" s="8" t="n">
-        <v>0.07199999999999999</v>
+        <v>72</v>
       </c>
       <c r="AJ5" s="8" t="n">
-        <v>0.068</v>
+        <v>68</v>
       </c>
       <c r="AK5" s="8" t="n">
-        <v>0.067</v>
+        <v>67</v>
       </c>
       <c r="AL5" s="8" t="n">
-        <v>0.055</v>
+        <v>55</v>
       </c>
       <c r="AM5" s="8" t="n">
-        <v>0.061</v>
+        <v>61</v>
       </c>
       <c r="AN5" s="8" t="n">
-        <v>0.041</v>
+        <v>41</v>
       </c>
       <c r="AO5" s="8" t="n">
-        <v>0.044</v>
+        <v>44</v>
       </c>
       <c r="AP5" s="8" t="n">
-        <v>0.04</v>
+        <v>40</v>
       </c>
       <c r="AQ5" s="8" t="n">
-        <v>0.058</v>
+        <v>58</v>
       </c>
       <c r="AR5" s="8" t="n">
-        <v>0.058</v>
+        <v>58</v>
       </c>
       <c r="AS5" s="8" t="n">
-        <v>0.051</v>
+        <v>51</v>
       </c>
       <c r="AT5" s="8" t="n">
-        <v>0.041</v>
+        <v>41</v>
       </c>
       <c r="AU5" s="8" t="n">
-        <v>0.024</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -2902,142 +2791,142 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>0.216</v>
+        <v>216</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>0.212</v>
+        <v>212</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>0.183</v>
+        <v>183</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>0.278</v>
+        <v>278</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.224</v>
+        <v>224</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>0.25</v>
+        <v>250</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>0.24</v>
+        <v>240</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.284</v>
+        <v>284</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>0.296</v>
+        <v>296</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>0.277</v>
+        <v>277</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>0.311</v>
+        <v>311</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>0.317</v>
+        <v>317</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>0.313</v>
+        <v>313</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>0.37</v>
+        <v>370</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>0.259</v>
+        <v>259</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>0.358</v>
+        <v>358</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>0.305</v>
+        <v>305</v>
       </c>
       <c r="S6" s="8" t="n">
-        <v>0.387</v>
+        <v>387</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>0.324</v>
+        <v>324</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>0.324</v>
+        <v>324</v>
       </c>
       <c r="V6" s="8" t="n">
-        <v>0.345</v>
+        <v>345</v>
       </c>
       <c r="W6" s="8" t="n">
-        <v>0.271</v>
+        <v>271</v>
       </c>
       <c r="X6" s="8" t="n">
-        <v>0.343</v>
+        <v>343</v>
       </c>
       <c r="Y6" s="8" t="n">
-        <v>0.357</v>
+        <v>357</v>
       </c>
       <c r="Z6" s="8" t="n">
-        <v>0.499</v>
+        <v>499</v>
       </c>
       <c r="AA6" s="8" t="n">
-        <v>0.49</v>
+        <v>490</v>
       </c>
       <c r="AB6" s="8" t="n">
-        <v>0.535</v>
+        <v>535</v>
       </c>
       <c r="AC6" s="8" t="n">
-        <v>0.486</v>
+        <v>486</v>
       </c>
       <c r="AD6" s="8" t="n">
-        <v>0.527</v>
+        <v>527</v>
       </c>
       <c r="AE6" s="8" t="n">
-        <v>0.432</v>
+        <v>432</v>
       </c>
       <c r="AF6" s="8" t="n">
-        <v>0.344</v>
+        <v>344</v>
       </c>
       <c r="AG6" s="8" t="n">
-        <v>0.39</v>
+        <v>390</v>
       </c>
       <c r="AH6" s="8" t="n">
-        <v>0.355</v>
+        <v>355</v>
       </c>
       <c r="AI6" s="8" t="n">
-        <v>0.341</v>
+        <v>341</v>
       </c>
       <c r="AJ6" s="8" t="n">
-        <v>0.34</v>
+        <v>340</v>
       </c>
       <c r="AK6" s="8" t="n">
-        <v>0.318</v>
+        <v>318</v>
       </c>
       <c r="AL6" s="8" t="n">
-        <v>0.3</v>
+        <v>300</v>
       </c>
       <c r="AM6" s="8" t="n">
-        <v>0.3</v>
+        <v>300</v>
       </c>
       <c r="AN6" s="8" t="n">
-        <v>0.233</v>
+        <v>233</v>
       </c>
       <c r="AO6" s="8" t="n">
-        <v>0.237</v>
+        <v>237</v>
       </c>
       <c r="AP6" s="8" t="n">
-        <v>0.187</v>
+        <v>187</v>
       </c>
       <c r="AQ6" s="8" t="n">
-        <v>0.235</v>
+        <v>235</v>
       </c>
       <c r="AR6" s="8" t="n">
-        <v>0.382</v>
+        <v>382</v>
       </c>
       <c r="AS6" s="8" t="n">
-        <v>0.346</v>
+        <v>346</v>
       </c>
       <c r="AT6" s="8" t="n">
-        <v>0.263</v>
+        <v>263</v>
       </c>
       <c r="AU6" s="8" t="n">
-        <v>0.161</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7">
@@ -3047,142 +2936,142 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.328</v>
+        <v>328</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>0.261</v>
+        <v>261</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>0.313</v>
+        <v>313</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>0.351</v>
+        <v>351</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0.339</v>
+        <v>339</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>0.426</v>
+        <v>426</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>0.542</v>
+        <v>542</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.348</v>
+        <v>348</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>0.574</v>
+        <v>574</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>0.428</v>
+        <v>428</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>0.552</v>
+        <v>552</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>0.66</v>
+        <v>660</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>0.517</v>
+        <v>517</v>
       </c>
       <c r="O7" s="8" t="n">
-        <v>0.662</v>
+        <v>662</v>
       </c>
       <c r="P7" s="8" t="n">
-        <v>0.745</v>
+        <v>745</v>
       </c>
       <c r="Q7" s="8" t="n">
-        <v>0.629</v>
+        <v>629</v>
       </c>
       <c r="R7" s="8" t="n">
-        <v>0.704</v>
+        <v>704</v>
       </c>
       <c r="S7" s="8" t="n">
-        <v>0.732</v>
+        <v>732</v>
       </c>
       <c r="T7" s="8" t="n">
-        <v>0.664</v>
+        <v>664</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>0.734</v>
+        <v>734</v>
       </c>
       <c r="V7" s="8" t="n">
-        <v>0.701</v>
+        <v>701</v>
       </c>
       <c r="W7" s="8" t="n">
-        <v>0.702</v>
+        <v>702</v>
       </c>
       <c r="X7" s="8" t="n">
-        <v>0.701</v>
+        <v>701</v>
       </c>
       <c r="Y7" s="8" t="n">
-        <v>0.822</v>
+        <v>822</v>
       </c>
       <c r="Z7" s="8" t="n">
-        <v>0.899</v>
+        <v>899</v>
       </c>
       <c r="AA7" s="8" t="n">
-        <v>1.172</v>
+        <v>1172</v>
       </c>
       <c r="AB7" s="8" t="n">
-        <v>0.853</v>
+        <v>853</v>
       </c>
       <c r="AC7" s="8" t="n">
-        <v>1.203</v>
+        <v>1203</v>
       </c>
       <c r="AD7" s="8" t="n">
-        <v>1.148</v>
+        <v>1148</v>
       </c>
       <c r="AE7" s="8" t="n">
-        <v>0.907</v>
+        <v>907</v>
       </c>
       <c r="AF7" s="8" t="n">
-        <v>0.756</v>
+        <v>756</v>
       </c>
       <c r="AG7" s="8" t="n">
-        <v>0.836</v>
+        <v>836</v>
       </c>
       <c r="AH7" s="8" t="n">
-        <v>0.871</v>
+        <v>871</v>
       </c>
       <c r="AI7" s="8" t="n">
-        <v>1.052</v>
+        <v>1052</v>
       </c>
       <c r="AJ7" s="8" t="n">
-        <v>0.635</v>
+        <v>635</v>
       </c>
       <c r="AK7" s="8" t="n">
-        <v>0.655</v>
+        <v>655</v>
       </c>
       <c r="AL7" s="8" t="n">
-        <v>0.832</v>
+        <v>832</v>
       </c>
       <c r="AM7" s="8" t="n">
-        <v>0.721</v>
+        <v>721</v>
       </c>
       <c r="AN7" s="8" t="n">
-        <v>0.6860000000000001</v>
+        <v>686</v>
       </c>
       <c r="AO7" s="8" t="n">
-        <v>0.5610000000000001</v>
+        <v>561</v>
       </c>
       <c r="AP7" s="8" t="n">
-        <v>0.54</v>
+        <v>540</v>
       </c>
       <c r="AQ7" s="8" t="n">
-        <v>0.755</v>
+        <v>755</v>
       </c>
       <c r="AR7" s="8" t="n">
-        <v>0.88</v>
+        <v>880</v>
       </c>
       <c r="AS7" s="8" t="n">
-        <v>0.707</v>
+        <v>707</v>
       </c>
       <c r="AT7" s="8" t="n">
-        <v>0.638</v>
+        <v>638</v>
       </c>
       <c r="AU7" s="8" t="n">
-        <v>0.509</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -3192,142 +3081,142 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>0.367</v>
+        <v>367</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>0.351</v>
+        <v>351</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>0.298</v>
+        <v>298</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>0.414</v>
+        <v>414</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.526</v>
+        <v>526</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>0.55</v>
+        <v>550</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>0.303</v>
+        <v>303</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.48</v>
+        <v>480</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>0.476</v>
+        <v>476</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>0.352</v>
+        <v>352</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>0.666</v>
+        <v>666</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>0.511</v>
+        <v>511</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>0.361</v>
+        <v>361</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>0.699</v>
+        <v>699</v>
       </c>
       <c r="P8" s="8" t="n">
-        <v>0.618</v>
+        <v>618</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>0.9320000000000001</v>
+        <v>932</v>
       </c>
       <c r="R8" s="8" t="n">
-        <v>0.66</v>
+        <v>660</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>0.8</v>
+        <v>800</v>
       </c>
       <c r="T8" s="8" t="n">
-        <v>0.602</v>
+        <v>602</v>
       </c>
       <c r="U8" s="8" t="n">
-        <v>0.784</v>
+        <v>784</v>
       </c>
       <c r="V8" s="8" t="n">
-        <v>0.636</v>
+        <v>636</v>
       </c>
       <c r="W8" s="8" t="n">
-        <v>0.52</v>
+        <v>520</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>0.8100000000000001</v>
+        <v>810</v>
       </c>
       <c r="Y8" s="8" t="n">
-        <v>1.038</v>
+        <v>1038</v>
       </c>
       <c r="Z8" s="8" t="n">
-        <v>1.129</v>
+        <v>1129</v>
       </c>
       <c r="AA8" s="8" t="n">
-        <v>0.872</v>
+        <v>872</v>
       </c>
       <c r="AB8" s="8" t="n">
-        <v>1.391</v>
+        <v>1391</v>
       </c>
       <c r="AC8" s="8" t="n">
-        <v>1.055</v>
+        <v>1055</v>
       </c>
       <c r="AD8" s="8" t="n">
-        <v>1.556</v>
+        <v>1556</v>
       </c>
       <c r="AE8" s="8" t="n">
-        <v>1.268</v>
+        <v>1268</v>
       </c>
       <c r="AF8" s="8" t="n">
-        <v>0.998</v>
+        <v>998</v>
       </c>
       <c r="AG8" s="8" t="n">
-        <v>1.142</v>
+        <v>1142</v>
       </c>
       <c r="AH8" s="8" t="n">
-        <v>0.908</v>
+        <v>908</v>
       </c>
       <c r="AI8" s="8" t="n">
-        <v>0.838</v>
+        <v>838</v>
       </c>
       <c r="AJ8" s="8" t="n">
-        <v>0.8070000000000001</v>
+        <v>807</v>
       </c>
       <c r="AK8" s="8" t="n">
-        <v>0.709</v>
+        <v>709</v>
       </c>
       <c r="AL8" s="8" t="n">
-        <v>0.848</v>
+        <v>848</v>
       </c>
       <c r="AM8" s="8" t="n">
-        <v>0.964</v>
+        <v>964</v>
       </c>
       <c r="AN8" s="8" t="n">
-        <v>0.742</v>
+        <v>742</v>
       </c>
       <c r="AO8" s="8" t="n">
-        <v>0.875</v>
+        <v>875</v>
       </c>
       <c r="AP8" s="8" t="n">
-        <v>0.632</v>
+        <v>632</v>
       </c>
       <c r="AQ8" s="8" t="n">
-        <v>0.867</v>
+        <v>867</v>
       </c>
       <c r="AR8" s="8" t="n">
-        <v>1.163</v>
+        <v>1163</v>
       </c>
       <c r="AS8" s="8" t="n">
-        <v>0.965</v>
+        <v>965</v>
       </c>
       <c r="AT8" s="8" t="n">
-        <v>0.784</v>
+        <v>784</v>
       </c>
       <c r="AU8" s="8" t="n">
-        <v>1.033</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="9">
@@ -3337,142 +3226,142 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>0.37</v>
+        <v>370</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>0.288</v>
+        <v>288</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>0.334</v>
+        <v>334</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>0.352</v>
+        <v>352</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.64</v>
+        <v>640</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>0.214</v>
+        <v>214</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>0.331</v>
+        <v>331</v>
       </c>
       <c r="I9" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>0.279</v>
+        <v>279</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>0.362</v>
+        <v>362</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0.5600000000000001</v>
+        <v>560</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>0.654</v>
+        <v>654</v>
       </c>
       <c r="N9" s="8" t="n">
-        <v>0.434</v>
+        <v>434</v>
       </c>
       <c r="O9" s="8" t="n">
-        <v>0.719</v>
+        <v>719</v>
       </c>
       <c r="P9" s="8" t="n">
-        <v>0.923</v>
+        <v>923</v>
       </c>
       <c r="Q9" s="8" t="n">
-        <v>0.431</v>
+        <v>431</v>
       </c>
       <c r="R9" s="8" t="n">
-        <v>0.436</v>
+        <v>436</v>
       </c>
       <c r="S9" s="8" t="n">
-        <v>0.673</v>
+        <v>673</v>
       </c>
       <c r="T9" s="8" t="n">
-        <v>0.871</v>
+        <v>871</v>
       </c>
       <c r="U9" s="8" t="n">
-        <v>0.59</v>
+        <v>590</v>
       </c>
       <c r="V9" s="8" t="n">
-        <v>0.988</v>
+        <v>988</v>
       </c>
       <c r="W9" s="8" t="n">
-        <v>1.049</v>
+        <v>1049</v>
       </c>
       <c r="X9" s="8" t="n">
-        <v>0.737</v>
+        <v>737</v>
       </c>
       <c r="Y9" s="8" t="n">
-        <v>1.003</v>
+        <v>1003</v>
       </c>
       <c r="Z9" s="8" t="n">
-        <v>1.257</v>
+        <v>1257</v>
       </c>
       <c r="AA9" s="8" t="n">
-        <v>1.784</v>
+        <v>1784</v>
       </c>
       <c r="AB9" s="8" t="n">
-        <v>1.955</v>
+        <v>1955</v>
       </c>
       <c r="AC9" s="8" t="n">
-        <v>2.077</v>
+        <v>2077</v>
       </c>
       <c r="AD9" s="8" t="n">
-        <v>2.298</v>
+        <v>2298</v>
       </c>
       <c r="AE9" s="8" t="n">
-        <v>2.269</v>
+        <v>2269</v>
       </c>
       <c r="AF9" s="8" t="n">
-        <v>0.754</v>
+        <v>754</v>
       </c>
       <c r="AG9" s="8" t="n">
-        <v>0.846</v>
+        <v>846</v>
       </c>
       <c r="AH9" s="8" t="n">
-        <v>1.268</v>
+        <v>1268</v>
       </c>
       <c r="AI9" s="8" t="n">
-        <v>1.104</v>
+        <v>1104</v>
       </c>
       <c r="AJ9" s="8" t="n">
-        <v>1.039</v>
+        <v>1039</v>
       </c>
       <c r="AK9" s="8" t="n">
-        <v>0.5649999999999999</v>
+        <v>565</v>
       </c>
       <c r="AL9" s="8" t="n">
-        <v>0.702</v>
+        <v>702</v>
       </c>
       <c r="AM9" s="8" t="n">
-        <v>1.07</v>
+        <v>1070</v>
       </c>
       <c r="AN9" s="8" t="n">
-        <v>0.671</v>
+        <v>671</v>
       </c>
       <c r="AO9" s="8" t="n">
-        <v>1.194</v>
+        <v>1194</v>
       </c>
       <c r="AP9" s="8" t="n">
-        <v>1.088</v>
+        <v>1088</v>
       </c>
       <c r="AQ9" s="8" t="n">
-        <v>0.524</v>
+        <v>524</v>
       </c>
       <c r="AR9" s="8" t="n">
-        <v>0.826</v>
+        <v>826</v>
       </c>
       <c r="AS9" s="8" t="n">
-        <v>1.392</v>
+        <v>1392</v>
       </c>
       <c r="AT9" s="8" t="n">
-        <v>1.019</v>
+        <v>1019</v>
       </c>
       <c r="AU9" s="8" t="n">
-        <v>0.899</v>
+        <v>899</v>
       </c>
     </row>
     <row r="10">
@@ -3482,142 +3371,142 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.1</v>
+        <v>100</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>0.15</v>
+        <v>150</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>0.377</v>
+        <v>377</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>0.208</v>
+        <v>208</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0.169</v>
+        <v>169</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>0.227</v>
+        <v>227</v>
       </c>
       <c r="H10" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0.226</v>
+        <v>226</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>0.202</v>
+        <v>202</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>0.232</v>
+        <v>232</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>0.265</v>
+        <v>265</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>0.511</v>
+        <v>511</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>0.579</v>
+        <v>579</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>0.331</v>
+        <v>331</v>
       </c>
       <c r="P10" s="8" t="n">
-        <v>0.25</v>
+        <v>250</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>0.607</v>
+        <v>607</v>
       </c>
       <c r="R10" s="8" t="n">
-        <v>0.1</v>
+        <v>100</v>
       </c>
       <c r="S10" s="8" t="n">
-        <v>0.754</v>
+        <v>754</v>
       </c>
       <c r="T10" s="8" t="n">
-        <v>0.582</v>
+        <v>582</v>
       </c>
       <c r="U10" s="8" t="n">
-        <v>0.8169999999999999</v>
+        <v>817</v>
       </c>
       <c r="V10" s="8" t="n">
-        <v>0.845</v>
+        <v>845</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>0.353</v>
+        <v>353</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>0.883</v>
+        <v>883</v>
       </c>
       <c r="Y10" s="8" t="n">
-        <v>1.396</v>
+        <v>1396</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>1.071</v>
+        <v>1071</v>
       </c>
       <c r="AA10" s="8" t="n">
-        <v>1.757</v>
+        <v>1757</v>
       </c>
       <c r="AB10" s="8" t="n">
-        <v>2.199</v>
+        <v>2199</v>
       </c>
       <c r="AC10" s="8" t="n">
-        <v>2.38</v>
+        <v>2380</v>
       </c>
       <c r="AD10" s="8" t="n">
-        <v>3.64</v>
+        <v>3640</v>
       </c>
       <c r="AE10" s="8" t="n">
-        <v>2.028</v>
+        <v>2028</v>
       </c>
       <c r="AF10" s="8" t="n">
-        <v>0.902</v>
+        <v>902</v>
       </c>
       <c r="AG10" s="8" t="n">
-        <v>1.333</v>
+        <v>1333</v>
       </c>
       <c r="AH10" s="8" t="n">
-        <v>0.358</v>
+        <v>358</v>
       </c>
       <c r="AI10" s="8" t="n">
-        <v>0.61</v>
+        <v>610</v>
       </c>
       <c r="AJ10" s="8" t="n">
-        <v>0.483</v>
+        <v>483</v>
       </c>
       <c r="AK10" s="8" t="n">
-        <v>1.347</v>
+        <v>1347</v>
       </c>
       <c r="AL10" s="8" t="n">
-        <v>0.253</v>
+        <v>253</v>
       </c>
       <c r="AM10" s="8" t="n">
-        <v>0.831</v>
+        <v>831</v>
       </c>
       <c r="AN10" s="8" t="n">
-        <v>1.049</v>
+        <v>1049</v>
       </c>
       <c r="AO10" s="8" t="n">
-        <v>0.836</v>
+        <v>836</v>
       </c>
       <c r="AP10" s="8" t="n">
-        <v>0.71</v>
+        <v>710</v>
       </c>
       <c r="AQ10" s="8" t="n">
-        <v>0.785</v>
+        <v>785</v>
       </c>
       <c r="AR10" s="8" t="n">
-        <v>1.109</v>
+        <v>1109</v>
       </c>
       <c r="AS10" s="8" t="n">
-        <v>0.587</v>
+        <v>587</v>
       </c>
       <c r="AT10" s="8" t="n">
-        <v>1.208</v>
+        <v>1208</v>
       </c>
       <c r="AU10" s="8" t="n">
-        <v>1.579</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="11">
@@ -3627,142 +3516,142 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>0.25</v>
+        <v>250</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>0.5</v>
+        <v>500</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>0.32</v>
+        <v>320</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>0.363</v>
+        <v>363</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>0.528</v>
+        <v>528</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>0.7</v>
+        <v>700</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>0.275</v>
+        <v>275</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>1.2</v>
+        <v>1200</v>
       </c>
       <c r="J11" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>0.899</v>
+        <v>899</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0.385</v>
+        <v>385</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>0.617</v>
+        <v>617</v>
       </c>
       <c r="N11" s="8" t="n">
         <v>0</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>0.25</v>
+        <v>250</v>
       </c>
       <c r="P11" s="8" t="n">
-        <v>0.25</v>
+        <v>250</v>
       </c>
       <c r="Q11" s="8" t="n">
         <v>0</v>
       </c>
       <c r="R11" s="8" t="n">
-        <v>1.954</v>
+        <v>1954</v>
       </c>
       <c r="S11" s="8" t="n">
-        <v>1.632</v>
+        <v>1632</v>
       </c>
       <c r="T11" s="8" t="n">
-        <v>1.21</v>
+        <v>1210</v>
       </c>
       <c r="U11" s="8" t="n">
-        <v>0.655</v>
+        <v>655</v>
       </c>
       <c r="V11" s="8" t="n">
-        <v>0.5</v>
+        <v>500</v>
       </c>
       <c r="W11" s="8" t="n">
-        <v>0.671</v>
+        <v>671</v>
       </c>
       <c r="X11" s="8" t="n">
-        <v>1.097</v>
+        <v>1097</v>
       </c>
       <c r="Y11" s="8" t="n">
-        <v>0.31</v>
+        <v>310</v>
       </c>
       <c r="Z11" s="8" t="n">
-        <v>3.183</v>
+        <v>3183</v>
       </c>
       <c r="AA11" s="8" t="n">
-        <v>4.11</v>
+        <v>4110</v>
       </c>
       <c r="AB11" s="8" t="n">
-        <v>4.011</v>
+        <v>4011</v>
       </c>
       <c r="AC11" s="8" t="n">
-        <v>3.045</v>
+        <v>3045</v>
       </c>
       <c r="AD11" s="8" t="n">
-        <v>3.385</v>
+        <v>3385</v>
       </c>
       <c r="AE11" s="8" t="n">
-        <v>2.028</v>
+        <v>2028</v>
       </c>
       <c r="AF11" s="8" t="n">
-        <v>0.594</v>
+        <v>594</v>
       </c>
       <c r="AG11" s="8" t="n">
         <v>0</v>
       </c>
       <c r="AH11" s="8" t="n">
-        <v>0.25</v>
+        <v>250</v>
       </c>
       <c r="AI11" s="8" t="n">
-        <v>0.25</v>
+        <v>250</v>
       </c>
       <c r="AJ11" s="8" t="n">
-        <v>2.331</v>
+        <v>2331</v>
       </c>
       <c r="AK11" s="8" t="n">
-        <v>1.635</v>
+        <v>1635</v>
       </c>
       <c r="AL11" s="8" t="n">
-        <v>1.013</v>
+        <v>1013</v>
       </c>
       <c r="AM11" s="8" t="n">
-        <v>2.001</v>
+        <v>2001</v>
       </c>
       <c r="AN11" s="8" t="n">
-        <v>0.8179999999999999</v>
+        <v>818</v>
       </c>
       <c r="AO11" s="8" t="n">
-        <v>0.637</v>
+        <v>637</v>
       </c>
       <c r="AP11" s="8" t="n">
-        <v>1.511</v>
+        <v>1511</v>
       </c>
       <c r="AQ11" s="8" t="n">
-        <v>0.5</v>
+        <v>500</v>
       </c>
       <c r="AR11" s="8" t="n">
-        <v>4.36</v>
+        <v>4360</v>
       </c>
       <c r="AS11" s="8" t="n">
-        <v>2.403</v>
+        <v>2403</v>
       </c>
       <c r="AT11" s="8" t="n">
-        <v>3.7</v>
+        <v>3700</v>
       </c>
       <c r="AU11" s="8" t="n">
-        <v>5.2</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="12">
@@ -3772,142 +3661,142 @@
         </is>
       </c>
       <c r="B12" s="10" t="n">
-        <v>1.72</v>
+        <v>1720</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1.837</v>
+        <v>1837</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1.906</v>
+        <v>1906</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>2.034</v>
+        <v>2034</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>2.517</v>
+        <v>2517</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>2.442</v>
+        <v>2442</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>1.766</v>
+        <v>1766</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>2.625</v>
+        <v>2625</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>1.909</v>
+        <v>1909</v>
       </c>
       <c r="K12" s="10" t="n">
-        <v>2.634</v>
+        <v>2634</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>2.814</v>
+        <v>2814</v>
       </c>
       <c r="M12" s="10" t="n">
-        <v>3.351</v>
+        <v>3351</v>
       </c>
       <c r="N12" s="10" t="n">
-        <v>2.301</v>
+        <v>2301</v>
       </c>
       <c r="O12" s="10" t="n">
-        <v>3.133</v>
+        <v>3133</v>
       </c>
       <c r="P12" s="10" t="n">
-        <v>3.129</v>
+        <v>3129</v>
       </c>
       <c r="Q12" s="10" t="n">
-        <v>3.054</v>
+        <v>3054</v>
       </c>
       <c r="R12" s="10" t="n">
-        <v>4.246</v>
+        <v>4246</v>
       </c>
       <c r="S12" s="10" t="n">
-        <v>5.077</v>
+        <v>5077</v>
       </c>
       <c r="T12" s="10" t="n">
-        <v>4.336</v>
+        <v>4336</v>
       </c>
       <c r="U12" s="10" t="n">
-        <v>3.987</v>
+        <v>3987</v>
       </c>
       <c r="V12" s="10" t="n">
-        <v>4.121</v>
+        <v>4121</v>
       </c>
       <c r="W12" s="10" t="n">
-        <v>3.667</v>
+        <v>3667</v>
       </c>
       <c r="X12" s="10" t="n">
-        <v>4.648</v>
+        <v>4648</v>
       </c>
       <c r="Y12" s="10" t="n">
-        <v>5.028</v>
+        <v>5028</v>
       </c>
       <c r="Z12" s="10" t="n">
-        <v>8.169</v>
+        <v>8169</v>
       </c>
       <c r="AA12" s="10" t="n">
-        <v>10.304</v>
+        <v>10304</v>
       </c>
       <c r="AB12" s="10" t="n">
-        <v>11.053</v>
+        <v>11053</v>
       </c>
       <c r="AC12" s="10" t="n">
-        <v>10.364</v>
+        <v>10364</v>
       </c>
       <c r="AD12" s="10" t="n">
-        <v>12.672</v>
+        <v>12672</v>
       </c>
       <c r="AE12" s="10" t="n">
-        <v>9.042</v>
+        <v>9042</v>
       </c>
       <c r="AF12" s="10" t="n">
-        <v>4.418</v>
+        <v>4418</v>
       </c>
       <c r="AG12" s="10" t="n">
-        <v>4.633</v>
+        <v>4633</v>
       </c>
       <c r="AH12" s="10" t="n">
-        <v>4.083</v>
+        <v>4083</v>
       </c>
       <c r="AI12" s="10" t="n">
-        <v>4.267</v>
+        <v>4267</v>
       </c>
       <c r="AJ12" s="10" t="n">
-        <v>5.703</v>
+        <v>5703</v>
       </c>
       <c r="AK12" s="10" t="n">
-        <v>5.295</v>
+        <v>5295</v>
       </c>
       <c r="AL12" s="10" t="n">
-        <v>4.002</v>
+        <v>4002</v>
       </c>
       <c r="AM12" s="10" t="n">
-        <v>5.947</v>
+        <v>5947</v>
       </c>
       <c r="AN12" s="10" t="n">
-        <v>4.24</v>
+        <v>4240</v>
       </c>
       <c r="AO12" s="10" t="n">
-        <v>4.384</v>
+        <v>4384</v>
       </c>
       <c r="AP12" s="10" t="n">
-        <v>4.707</v>
+        <v>4707</v>
       </c>
       <c r="AQ12" s="10" t="n">
-        <v>3.725</v>
+        <v>3725</v>
       </c>
       <c r="AR12" s="10" t="n">
-        <v>8.779</v>
+        <v>8779</v>
       </c>
       <c r="AS12" s="10" t="n">
-        <v>6.451</v>
+        <v>6451</v>
       </c>
       <c r="AT12" s="10" t="n">
-        <v>7.653</v>
+        <v>7653</v>
       </c>
       <c r="AU12" s="10" t="n">
-        <v>9.404</v>
+        <v>9404</v>
       </c>
     </row>
   </sheetData>
@@ -3925,18 +3814,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3949,7 +3838,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AI startups (tag: Artificial Intelligence). By stage, $B. 2026 = YTD.</t>
+          <t>AI startups (tag: Artificial Intelligence). By stage, $m. 2026 = to 25 June 2026.</t>
         </is>
       </c>
     </row>
@@ -4027,40 +3916,40 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>0.039</v>
+        <v>39</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>0.037</v>
+        <v>37</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>0.049</v>
+        <v>49</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>0.058</v>
+        <v>58</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>0.052</v>
+        <v>52</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>0.057</v>
+        <v>57</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0.073</v>
+        <v>73</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.051</v>
+        <v>51</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>0.058</v>
+        <v>58</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>0.042</v>
+        <v>42</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0.05</v>
+        <v>50</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>0.017</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -4070,40 +3959,40 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>0.108</v>
+        <v>108</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>0.173</v>
+        <v>173</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>0.261</v>
+        <v>261</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>0.22</v>
+        <v>220</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.267</v>
+        <v>267</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>0.255</v>
+        <v>255</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>0.343</v>
+        <v>343</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.333</v>
+        <v>333</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>0.299</v>
+        <v>299</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>0.275</v>
+        <v>275</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>0.298</v>
+        <v>298</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>0.136</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7">
@@ -4113,40 +4002,40 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.154</v>
+        <v>154</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>0.201</v>
+        <v>201</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>0.362</v>
+        <v>362</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>0.494</v>
+        <v>494</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0.741</v>
+        <v>741</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>0.604</v>
+        <v>604</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>0.857</v>
+        <v>857</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.78</v>
+        <v>780</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>0.588</v>
+        <v>588</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>0.772</v>
+        <v>772</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>0.881</v>
+        <v>881</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>0.476</v>
+        <v>476</v>
       </c>
     </row>
     <row r="8">
@@ -4156,40 +4045,40 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>0.171</v>
+        <v>171</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>0.173</v>
+        <v>173</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>0.309</v>
+        <v>309</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>0.47</v>
+        <v>470</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.538</v>
+        <v>538</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>0.487</v>
+        <v>487</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>0.736</v>
+        <v>736</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>1.187</v>
+        <v>1187</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>0.784</v>
+        <v>784</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>0.923</v>
+        <v>923</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>1.061</v>
+        <v>1061</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>0.8179999999999999</v>
+        <v>818</v>
       </c>
     </row>
     <row r="9">
@@ -4199,40 +4088,40 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>0.18</v>
+        <v>180</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>0.145</v>
+        <v>145</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>0.235</v>
+        <v>235</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>0.226</v>
+        <v>226</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.373</v>
+        <v>373</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>0.699</v>
+        <v>699</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>0.664</v>
+        <v>664</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>1.03</v>
+        <v>1030</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>1.199</v>
+        <v>1199</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>1.036</v>
+        <v>1036</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>1.214</v>
+        <v>1214</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>1.106</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="10">
@@ -4242,40 +4131,40 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.1</v>
+        <v>100</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>0.126</v>
+        <v>126</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>0.203</v>
+        <v>203</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>0.547</v>
+        <v>547</v>
       </c>
       <c r="F10" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>0.983</v>
+        <v>983</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>1.702</v>
+        <v>1702</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>1.385</v>
+        <v>1385</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>0.584</v>
+        <v>584</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>0.661</v>
+        <v>661</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>1.542</v>
+        <v>1542</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>1.788</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="11">
@@ -4297,28 +4186,28 @@
         <v>0</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>0.99</v>
+        <v>990</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>0.5</v>
+        <v>500</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>0.782</v>
+        <v>782</v>
       </c>
       <c r="I11" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>0.25</v>
+        <v>250</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>1.55</v>
+        <v>1550</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>3.133</v>
+        <v>3133</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>8.25</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="12">
@@ -4328,40 +4217,40 @@
         </is>
       </c>
       <c r="B12" s="10" t="n">
-        <v>0.752</v>
+        <v>752</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>0.856</v>
+        <v>856</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1.42</v>
+        <v>1420</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>2.015</v>
+        <v>2015</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>2.961</v>
+        <v>2961</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>3.585</v>
+        <v>3585</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>5.157</v>
+        <v>5157</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>4.765</v>
+        <v>4765</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>3.762</v>
+        <v>3762</v>
       </c>
       <c r="K12" s="10" t="n">
-        <v>5.258</v>
+        <v>5258</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>8.178000000000001</v>
+        <v>8178</v>
       </c>
       <c r="M12" s="10" t="n">
-        <v>12.591</v>
+        <v>12591</v>
       </c>
     </row>
   </sheetData>
@@ -4379,52 +4268,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="10" customWidth="1" min="26" max="26"/>
-    <col width="10" customWidth="1" min="27" max="27"/>
-    <col width="10" customWidth="1" min="28" max="28"/>
-    <col width="10" customWidth="1" min="29" max="29"/>
-    <col width="10" customWidth="1" min="30" max="30"/>
-    <col width="10" customWidth="1" min="31" max="31"/>
-    <col width="10" customWidth="1" min="32" max="32"/>
-    <col width="10" customWidth="1" min="33" max="33"/>
-    <col width="10" customWidth="1" min="34" max="34"/>
-    <col width="10" customWidth="1" min="35" max="35"/>
-    <col width="10" customWidth="1" min="36" max="36"/>
-    <col width="10" customWidth="1" min="37" max="37"/>
-    <col width="10" customWidth="1" min="38" max="38"/>
-    <col width="10" customWidth="1" min="39" max="39"/>
-    <col width="10" customWidth="1" min="40" max="40"/>
-    <col width="10" customWidth="1" min="41" max="41"/>
-    <col width="10" customWidth="1" min="42" max="42"/>
-    <col width="10" customWidth="1" min="43" max="43"/>
-    <col width="10" customWidth="1" min="44" max="44"/>
-    <col width="10" customWidth="1" min="45" max="45"/>
-    <col width="10" customWidth="1" min="46" max="46"/>
-    <col width="10" customWidth="1" min="47" max="47"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="31" max="31"/>
+    <col width="11" customWidth="1" min="32" max="32"/>
+    <col width="11" customWidth="1" min="33" max="33"/>
+    <col width="11" customWidth="1" min="34" max="34"/>
+    <col width="11" customWidth="1" min="35" max="35"/>
+    <col width="11" customWidth="1" min="36" max="36"/>
+    <col width="11" customWidth="1" min="37" max="37"/>
+    <col width="11" customWidth="1" min="38" max="38"/>
+    <col width="11" customWidth="1" min="39" max="39"/>
+    <col width="11" customWidth="1" min="40" max="40"/>
+    <col width="11" customWidth="1" min="41" max="41"/>
+    <col width="11" customWidth="1" min="42" max="42"/>
+    <col width="11" customWidth="1" min="43" max="43"/>
+    <col width="11" customWidth="1" min="44" max="44"/>
+    <col width="11" customWidth="1" min="45" max="45"/>
+    <col width="11" customWidth="1" min="46" max="46"/>
+    <col width="11" customWidth="1" min="47" max="47"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4437,7 +4326,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AI startups. By stage, $B.</t>
+          <t>AI startups. By stage, $m.</t>
         </is>
       </c>
     </row>
@@ -4685,142 +4574,142 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>0.012</v>
+        <v>12</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>0.008</v>
+        <v>8</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>0.011</v>
+        <v>11</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>0.008</v>
+        <v>8</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>0.008999999999999999</v>
+        <v>9</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>0.007</v>
+        <v>7</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0.012</v>
+        <v>12</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.008999999999999999</v>
+        <v>9</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>0.016</v>
+        <v>16</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>0.012</v>
+        <v>12</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0.01</v>
+        <v>10</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>0.011</v>
+        <v>11</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>0.017</v>
+        <v>17</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>0.018</v>
+        <v>18</v>
       </c>
       <c r="P5" s="8" t="n">
-        <v>0.013</v>
+        <v>13</v>
       </c>
       <c r="Q5" s="8" t="n">
-        <v>0.01</v>
+        <v>10</v>
       </c>
       <c r="R5" s="8" t="n">
-        <v>0.015</v>
+        <v>15</v>
       </c>
       <c r="S5" s="8" t="n">
-        <v>0.015</v>
+        <v>15</v>
       </c>
       <c r="T5" s="8" t="n">
-        <v>0.01</v>
+        <v>10</v>
       </c>
       <c r="U5" s="8" t="n">
-        <v>0.012</v>
+        <v>12</v>
       </c>
       <c r="V5" s="8" t="n">
-        <v>0.016</v>
+        <v>16</v>
       </c>
       <c r="W5" s="8" t="n">
-        <v>0.016</v>
+        <v>16</v>
       </c>
       <c r="X5" s="8" t="n">
-        <v>0.011</v>
+        <v>11</v>
       </c>
       <c r="Y5" s="8" t="n">
-        <v>0.014</v>
+        <v>14</v>
       </c>
       <c r="Z5" s="8" t="n">
-        <v>0.022</v>
+        <v>22</v>
       </c>
       <c r="AA5" s="8" t="n">
-        <v>0.014</v>
+        <v>14</v>
       </c>
       <c r="AB5" s="8" t="n">
-        <v>0.017</v>
+        <v>17</v>
       </c>
       <c r="AC5" s="8" t="n">
-        <v>0.02</v>
+        <v>20</v>
       </c>
       <c r="AD5" s="8" t="n">
-        <v>0.015</v>
+        <v>15</v>
       </c>
       <c r="AE5" s="8" t="n">
-        <v>0.017</v>
+        <v>17</v>
       </c>
       <c r="AF5" s="8" t="n">
-        <v>0.008999999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG5" s="8" t="n">
-        <v>0.01</v>
+        <v>10</v>
       </c>
       <c r="AH5" s="8" t="n">
-        <v>0.014</v>
+        <v>14</v>
       </c>
       <c r="AI5" s="8" t="n">
-        <v>0.015</v>
+        <v>15</v>
       </c>
       <c r="AJ5" s="8" t="n">
-        <v>0.017</v>
+        <v>17</v>
       </c>
       <c r="AK5" s="8" t="n">
-        <v>0.012</v>
+        <v>12</v>
       </c>
       <c r="AL5" s="8" t="n">
-        <v>0.012</v>
+        <v>12</v>
       </c>
       <c r="AM5" s="8" t="n">
-        <v>0.013</v>
+        <v>13</v>
       </c>
       <c r="AN5" s="8" t="n">
-        <v>0.008999999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO5" s="8" t="n">
-        <v>0.008</v>
+        <v>8</v>
       </c>
       <c r="AP5" s="8" t="n">
-        <v>0.012</v>
+        <v>12</v>
       </c>
       <c r="AQ5" s="8" t="n">
-        <v>0.016</v>
+        <v>16</v>
       </c>
       <c r="AR5" s="8" t="n">
-        <v>0.013</v>
+        <v>13</v>
       </c>
       <c r="AS5" s="8" t="n">
-        <v>0.008</v>
+        <v>8</v>
       </c>
       <c r="AT5" s="8" t="n">
-        <v>0.015</v>
+        <v>15</v>
       </c>
       <c r="AU5" s="8" t="n">
-        <v>0.002</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -4830,142 +4719,142 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>0.022</v>
+        <v>22</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>0.025</v>
+        <v>25</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>0.028</v>
+        <v>28</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>0.033</v>
+        <v>33</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0.039</v>
+        <v>39</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>0.027</v>
+        <v>27</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>0.061</v>
+        <v>61</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.046</v>
+        <v>46</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>0.055</v>
+        <v>55</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>0.056</v>
+        <v>56</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>0.082</v>
+        <v>82</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>0.06900000000000001</v>
+        <v>69</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>0.062</v>
+        <v>62</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>0.057</v>
+        <v>57</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>0.043</v>
+        <v>43</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>0.058</v>
+        <v>58</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>0.076</v>
+        <v>76</v>
       </c>
       <c r="S6" s="8" t="n">
-        <v>0.07099999999999999</v>
+        <v>71</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>0.054</v>
+        <v>54</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>0.067</v>
+        <v>67</v>
       </c>
       <c r="V6" s="8" t="n">
-        <v>0.07000000000000001</v>
+        <v>70</v>
       </c>
       <c r="W6" s="8" t="n">
-        <v>0.052</v>
+        <v>52</v>
       </c>
       <c r="X6" s="8" t="n">
-        <v>0.062</v>
+        <v>62</v>
       </c>
       <c r="Y6" s="8" t="n">
-        <v>0.07000000000000001</v>
+        <v>70</v>
       </c>
       <c r="Z6" s="8" t="n">
-        <v>0.083</v>
+        <v>83</v>
       </c>
       <c r="AA6" s="8" t="n">
-        <v>0.08599999999999999</v>
+        <v>86</v>
       </c>
       <c r="AB6" s="8" t="n">
-        <v>0.076</v>
+        <v>76</v>
       </c>
       <c r="AC6" s="8" t="n">
-        <v>0.099</v>
+        <v>99</v>
       </c>
       <c r="AD6" s="8" t="n">
-        <v>0.126</v>
+        <v>126</v>
       </c>
       <c r="AE6" s="8" t="n">
-        <v>0.092</v>
+        <v>92</v>
       </c>
       <c r="AF6" s="8" t="n">
-        <v>0.051</v>
+        <v>51</v>
       </c>
       <c r="AG6" s="8" t="n">
-        <v>0.063</v>
+        <v>63</v>
       </c>
       <c r="AH6" s="8" t="n">
-        <v>0.059</v>
+        <v>59</v>
       </c>
       <c r="AI6" s="8" t="n">
-        <v>0.07099999999999999</v>
+        <v>71</v>
       </c>
       <c r="AJ6" s="8" t="n">
-        <v>0.081</v>
+        <v>81</v>
       </c>
       <c r="AK6" s="8" t="n">
-        <v>0.08799999999999999</v>
+        <v>88</v>
       </c>
       <c r="AL6" s="8" t="n">
-        <v>0.075</v>
+        <v>75</v>
       </c>
       <c r="AM6" s="8" t="n">
-        <v>0.07000000000000001</v>
+        <v>70</v>
       </c>
       <c r="AN6" s="8" t="n">
-        <v>0.066</v>
+        <v>66</v>
       </c>
       <c r="AO6" s="8" t="n">
-        <v>0.064</v>
+        <v>64</v>
       </c>
       <c r="AP6" s="8" t="n">
-        <v>0.057</v>
+        <v>57</v>
       </c>
       <c r="AQ6" s="8" t="n">
-        <v>0.057</v>
+        <v>57</v>
       </c>
       <c r="AR6" s="8" t="n">
-        <v>0.06900000000000001</v>
+        <v>69</v>
       </c>
       <c r="AS6" s="8" t="n">
-        <v>0.114</v>
+        <v>114</v>
       </c>
       <c r="AT6" s="8" t="n">
-        <v>0.089</v>
+        <v>89</v>
       </c>
       <c r="AU6" s="8" t="n">
-        <v>0.047</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
@@ -4975,142 +4864,142 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.026</v>
+        <v>26</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>0.034</v>
+        <v>34</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>0.051</v>
+        <v>51</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>0.042</v>
+        <v>42</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0.036</v>
+        <v>36</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>0.05</v>
+        <v>50</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>0.082</v>
+        <v>82</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.034</v>
+        <v>34</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>0.08500000000000001</v>
+        <v>85</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>0.045</v>
+        <v>45</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>0.098</v>
+        <v>98</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>0.134</v>
+        <v>134</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>0.129</v>
+        <v>129</v>
       </c>
       <c r="O7" s="8" t="n">
-        <v>0.124</v>
+        <v>124</v>
       </c>
       <c r="P7" s="8" t="n">
-        <v>0.146</v>
+        <v>146</v>
       </c>
       <c r="Q7" s="8" t="n">
-        <v>0.095</v>
+        <v>95</v>
       </c>
       <c r="R7" s="8" t="n">
-        <v>0.197</v>
+        <v>197</v>
       </c>
       <c r="S7" s="8" t="n">
-        <v>0.205</v>
+        <v>205</v>
       </c>
       <c r="T7" s="8" t="n">
-        <v>0.121</v>
+        <v>121</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>0.218</v>
+        <v>218</v>
       </c>
       <c r="V7" s="8" t="n">
-        <v>0.153</v>
+        <v>153</v>
       </c>
       <c r="W7" s="8" t="n">
-        <v>0.167</v>
+        <v>167</v>
       </c>
       <c r="X7" s="8" t="n">
-        <v>0.128</v>
+        <v>128</v>
       </c>
       <c r="Y7" s="8" t="n">
-        <v>0.156</v>
+        <v>156</v>
       </c>
       <c r="Z7" s="8" t="n">
-        <v>0.171</v>
+        <v>171</v>
       </c>
       <c r="AA7" s="8" t="n">
-        <v>0.213</v>
+        <v>213</v>
       </c>
       <c r="AB7" s="8" t="n">
-        <v>0.164</v>
+        <v>164</v>
       </c>
       <c r="AC7" s="8" t="n">
-        <v>0.308</v>
+        <v>308</v>
       </c>
       <c r="AD7" s="8" t="n">
-        <v>0.235</v>
+        <v>235</v>
       </c>
       <c r="AE7" s="8" t="n">
-        <v>0.216</v>
+        <v>216</v>
       </c>
       <c r="AF7" s="8" t="n">
-        <v>0.126</v>
+        <v>126</v>
       </c>
       <c r="AG7" s="8" t="n">
-        <v>0.203</v>
+        <v>203</v>
       </c>
       <c r="AH7" s="8" t="n">
-        <v>0.152</v>
+        <v>152</v>
       </c>
       <c r="AI7" s="8" t="n">
-        <v>0.165</v>
+        <v>165</v>
       </c>
       <c r="AJ7" s="8" t="n">
-        <v>0.113</v>
+        <v>113</v>
       </c>
       <c r="AK7" s="8" t="n">
-        <v>0.157</v>
+        <v>157</v>
       </c>
       <c r="AL7" s="8" t="n">
-        <v>0.263</v>
+        <v>263</v>
       </c>
       <c r="AM7" s="8" t="n">
-        <v>0.161</v>
+        <v>161</v>
       </c>
       <c r="AN7" s="8" t="n">
-        <v>0.186</v>
+        <v>186</v>
       </c>
       <c r="AO7" s="8" t="n">
-        <v>0.163</v>
+        <v>163</v>
       </c>
       <c r="AP7" s="8" t="n">
-        <v>0.147</v>
+        <v>147</v>
       </c>
       <c r="AQ7" s="8" t="n">
-        <v>0.233</v>
+        <v>233</v>
       </c>
       <c r="AR7" s="8" t="n">
-        <v>0.258</v>
+        <v>258</v>
       </c>
       <c r="AS7" s="8" t="n">
-        <v>0.242</v>
+        <v>242</v>
       </c>
       <c r="AT7" s="8" t="n">
-        <v>0.345</v>
+        <v>345</v>
       </c>
       <c r="AU7" s="8" t="n">
-        <v>0.131</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8">
@@ -5120,142 +5009,142 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>0.094</v>
+        <v>94</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>0.03</v>
+        <v>30</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>0.046</v>
+        <v>46</v>
       </c>
       <c r="E8" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0.048</v>
+        <v>48</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>0.062</v>
+        <v>62</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0.063</v>
+        <v>63</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>0.06</v>
+        <v>60</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>0.07099999999999999</v>
+        <v>71</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>0.156</v>
+        <v>156</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>0.022</v>
+        <v>22</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>0.114</v>
+        <v>114</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>0.148</v>
+        <v>148</v>
       </c>
       <c r="P8" s="8" t="n">
-        <v>0.074</v>
+        <v>74</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>0.134</v>
+        <v>134</v>
       </c>
       <c r="R8" s="8" t="n">
-        <v>0.132</v>
+        <v>132</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>0.127</v>
+        <v>127</v>
       </c>
       <c r="T8" s="8" t="n">
-        <v>0.126</v>
+        <v>126</v>
       </c>
       <c r="U8" s="8" t="n">
-        <v>0.154</v>
+        <v>154</v>
       </c>
       <c r="V8" s="8" t="n">
-        <v>0.102</v>
+        <v>102</v>
       </c>
       <c r="W8" s="8" t="n">
-        <v>0.06900000000000001</v>
+        <v>69</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>0.119</v>
+        <v>119</v>
       </c>
       <c r="Y8" s="8" t="n">
-        <v>0.198</v>
+        <v>198</v>
       </c>
       <c r="Z8" s="8" t="n">
-        <v>0.138</v>
+        <v>138</v>
       </c>
       <c r="AA8" s="8" t="n">
-        <v>0.181</v>
+        <v>181</v>
       </c>
       <c r="AB8" s="8" t="n">
-        <v>0.221</v>
+        <v>221</v>
       </c>
       <c r="AC8" s="8" t="n">
-        <v>0.196</v>
+        <v>196</v>
       </c>
       <c r="AD8" s="8" t="n">
-        <v>0.51</v>
+        <v>510</v>
       </c>
       <c r="AE8" s="8" t="n">
-        <v>0.201</v>
+        <v>201</v>
       </c>
       <c r="AF8" s="8" t="n">
-        <v>0.227</v>
+        <v>227</v>
       </c>
       <c r="AG8" s="8" t="n">
-        <v>0.248</v>
+        <v>248</v>
       </c>
       <c r="AH8" s="8" t="n">
-        <v>0.188</v>
+        <v>188</v>
       </c>
       <c r="AI8" s="8" t="n">
-        <v>0.162</v>
+        <v>162</v>
       </c>
       <c r="AJ8" s="8" t="n">
-        <v>0.21</v>
+        <v>210</v>
       </c>
       <c r="AK8" s="8" t="n">
-        <v>0.225</v>
+        <v>225</v>
       </c>
       <c r="AL8" s="8" t="n">
-        <v>0.234</v>
+        <v>234</v>
       </c>
       <c r="AM8" s="8" t="n">
-        <v>0.236</v>
+        <v>236</v>
       </c>
       <c r="AN8" s="8" t="n">
-        <v>0.216</v>
+        <v>216</v>
       </c>
       <c r="AO8" s="8" t="n">
-        <v>0.237</v>
+        <v>237</v>
       </c>
       <c r="AP8" s="8" t="n">
-        <v>0.102</v>
+        <v>102</v>
       </c>
       <c r="AQ8" s="8" t="n">
-        <v>0.346</v>
+        <v>346</v>
       </c>
       <c r="AR8" s="8" t="n">
-        <v>0.343</v>
+        <v>343</v>
       </c>
       <c r="AS8" s="8" t="n">
-        <v>0.27</v>
+        <v>270</v>
       </c>
       <c r="AT8" s="8" t="n">
-        <v>0.463</v>
+        <v>463</v>
       </c>
       <c r="AU8" s="8" t="n">
-        <v>0.355</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9">
@@ -5271,19 +5160,19 @@
         <v>0</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>0.092</v>
+        <v>92</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>0.08699999999999999</v>
+        <v>87</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0.04</v>
+        <v>40</v>
       </c>
       <c r="G9" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>0.105</v>
+        <v>105</v>
       </c>
       <c r="I9" s="8" t="n">
         <v>0</v>
@@ -5292,13 +5181,13 @@
         <v>0</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>0.06</v>
+        <v>60</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0.125</v>
+        <v>125</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>0.05</v>
+        <v>50</v>
       </c>
       <c r="N9" s="8" t="n">
         <v>0</v>
@@ -5307,100 +5196,100 @@
         <v>0</v>
       </c>
       <c r="P9" s="8" t="n">
-        <v>0.05</v>
+        <v>50</v>
       </c>
       <c r="Q9" s="8" t="n">
-        <v>0.176</v>
+        <v>176</v>
       </c>
       <c r="R9" s="8" t="n">
         <v>0</v>
       </c>
       <c r="S9" s="8" t="n">
-        <v>0.132</v>
+        <v>132</v>
       </c>
       <c r="T9" s="8" t="n">
-        <v>0.145</v>
+        <v>145</v>
       </c>
       <c r="U9" s="8" t="n">
-        <v>0.096</v>
+        <v>96</v>
       </c>
       <c r="V9" s="8" t="n">
-        <v>0.114</v>
+        <v>114</v>
       </c>
       <c r="W9" s="8" t="n">
-        <v>0.336</v>
+        <v>336</v>
       </c>
       <c r="X9" s="8" t="n">
-        <v>0.115</v>
+        <v>115</v>
       </c>
       <c r="Y9" s="8" t="n">
-        <v>0.134</v>
+        <v>134</v>
       </c>
       <c r="Z9" s="8" t="n">
-        <v>0.047</v>
+        <v>47</v>
       </c>
       <c r="AA9" s="8" t="n">
-        <v>0.282</v>
+        <v>282</v>
       </c>
       <c r="AB9" s="8" t="n">
-        <v>0.185</v>
+        <v>185</v>
       </c>
       <c r="AC9" s="8" t="n">
-        <v>0.15</v>
+        <v>150</v>
       </c>
       <c r="AD9" s="8" t="n">
-        <v>0.35</v>
+        <v>350</v>
       </c>
       <c r="AE9" s="8" t="n">
-        <v>0.483</v>
+        <v>483</v>
       </c>
       <c r="AF9" s="8" t="n">
-        <v>0.04</v>
+        <v>40</v>
       </c>
       <c r="AG9" s="8" t="n">
-        <v>0.156</v>
+        <v>156</v>
       </c>
       <c r="AH9" s="8" t="n">
-        <v>0.301</v>
+        <v>301</v>
       </c>
       <c r="AI9" s="8" t="n">
-        <v>0.439</v>
+        <v>439</v>
       </c>
       <c r="AJ9" s="8" t="n">
-        <v>0.369</v>
+        <v>369</v>
       </c>
       <c r="AK9" s="8" t="n">
-        <v>0.09</v>
+        <v>90</v>
       </c>
       <c r="AL9" s="8" t="n">
-        <v>0.193</v>
+        <v>193</v>
       </c>
       <c r="AM9" s="8" t="n">
-        <v>0.404</v>
+        <v>404</v>
       </c>
       <c r="AN9" s="8" t="n">
-        <v>0.167</v>
+        <v>167</v>
       </c>
       <c r="AO9" s="8" t="n">
-        <v>0.272</v>
+        <v>272</v>
       </c>
       <c r="AP9" s="8" t="n">
-        <v>0.27</v>
+        <v>270</v>
       </c>
       <c r="AQ9" s="8" t="n">
-        <v>0.161</v>
+        <v>160</v>
       </c>
       <c r="AR9" s="8" t="n">
-        <v>0.357</v>
+        <v>357</v>
       </c>
       <c r="AS9" s="8" t="n">
-        <v>0.426</v>
+        <v>426</v>
       </c>
       <c r="AT9" s="8" t="n">
-        <v>0.719</v>
+        <v>719</v>
       </c>
       <c r="AU9" s="8" t="n">
-        <v>0.388</v>
+        <v>388</v>
       </c>
     </row>
     <row r="10">
@@ -5416,7 +5305,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>0.1</v>
+        <v>100</v>
       </c>
       <c r="E10" s="8" t="n">
         <v>0</v>
@@ -5431,7 +5320,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0.126</v>
+        <v>126</v>
       </c>
       <c r="J10" s="8" t="n">
         <v>0</v>
@@ -5443,19 +5332,19 @@
         <v>0</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>0.203</v>
+        <v>203</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>0.132</v>
+        <v>132</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>0.115</v>
+        <v>115</v>
       </c>
       <c r="P10" s="8" t="n">
-        <v>0.1</v>
+        <v>100</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>0.2</v>
+        <v>200</v>
       </c>
       <c r="R10" s="8" t="n">
         <v>0</v>
@@ -5470,82 +5359,82 @@
         <v>0</v>
       </c>
       <c r="V10" s="8" t="n">
-        <v>0.25</v>
+        <v>250</v>
       </c>
       <c r="W10" s="8" t="n">
-        <v>0.1</v>
+        <v>100</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>0.2</v>
+        <v>200</v>
       </c>
       <c r="Y10" s="8" t="n">
-        <v>0.433</v>
+        <v>433</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>0.25</v>
+        <v>250</v>
       </c>
       <c r="AA10" s="8" t="n">
-        <v>0.268</v>
+        <v>268</v>
       </c>
       <c r="AB10" s="8" t="n">
-        <v>0.8159999999999999</v>
+        <v>816</v>
       </c>
       <c r="AC10" s="8" t="n">
-        <v>0.368</v>
+        <v>368</v>
       </c>
       <c r="AD10" s="8" t="n">
-        <v>0.803</v>
+        <v>803</v>
       </c>
       <c r="AE10" s="8" t="n">
-        <v>0.358</v>
+        <v>358</v>
       </c>
       <c r="AF10" s="8" t="n">
         <v>0</v>
       </c>
       <c r="AG10" s="8" t="n">
-        <v>0.224</v>
+        <v>224</v>
       </c>
       <c r="AH10" s="8" t="n">
-        <v>0.14</v>
+        <v>140</v>
       </c>
       <c r="AI10" s="8" t="n">
-        <v>0.279</v>
+        <v>279</v>
       </c>
       <c r="AJ10" s="8" t="n">
         <v>0</v>
       </c>
       <c r="AK10" s="8" t="n">
-        <v>0.165</v>
+        <v>165</v>
       </c>
       <c r="AL10" s="8" t="n">
         <v>0</v>
       </c>
       <c r="AM10" s="8" t="n">
-        <v>0.106</v>
+        <v>106</v>
       </c>
       <c r="AN10" s="8" t="n">
-        <v>0.3</v>
+        <v>300</v>
       </c>
       <c r="AO10" s="8" t="n">
-        <v>0.255</v>
+        <v>255</v>
       </c>
       <c r="AP10" s="8" t="n">
-        <v>0.71</v>
+        <v>710</v>
       </c>
       <c r="AQ10" s="8" t="n">
-        <v>0.135</v>
+        <v>135</v>
       </c>
       <c r="AR10" s="8" t="n">
-        <v>0.597</v>
+        <v>597</v>
       </c>
       <c r="AS10" s="8" t="n">
-        <v>0.1</v>
+        <v>100</v>
       </c>
       <c r="AT10" s="8" t="n">
-        <v>0.948</v>
+        <v>948</v>
       </c>
       <c r="AU10" s="8" t="n">
-        <v>0.84</v>
+        <v>840</v>
       </c>
     </row>
     <row r="11">
@@ -5603,13 +5492,13 @@
         <v>0</v>
       </c>
       <c r="R11" s="8" t="n">
-        <v>0.44</v>
+        <v>440</v>
       </c>
       <c r="S11" s="8" t="n">
         <v>0</v>
       </c>
       <c r="T11" s="8" t="n">
-        <v>0.55</v>
+        <v>550</v>
       </c>
       <c r="U11" s="8" t="n">
         <v>0</v>
@@ -5621,7 +5510,7 @@
         <v>0</v>
       </c>
       <c r="X11" s="8" t="n">
-        <v>0.5</v>
+        <v>500</v>
       </c>
       <c r="Y11" s="8" t="n">
         <v>0</v>
@@ -5630,7 +5519,7 @@
         <v>0</v>
       </c>
       <c r="AA11" s="8" t="n">
-        <v>0.782</v>
+        <v>782</v>
       </c>
       <c r="AB11" s="8" t="n">
         <v>0</v>
@@ -5654,7 +5543,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="8" t="n">
-        <v>0.25</v>
+        <v>250</v>
       </c>
       <c r="AJ11" s="8" t="n">
         <v>0</v>
@@ -5666,31 +5555,31 @@
         <v>0</v>
       </c>
       <c r="AM11" s="8" t="n">
-        <v>1.05</v>
+        <v>1050</v>
       </c>
       <c r="AN11" s="8" t="n">
-        <v>0.5</v>
+        <v>500</v>
       </c>
       <c r="AO11" s="8" t="n">
         <v>0</v>
       </c>
       <c r="AP11" s="8" t="n">
-        <v>0.6</v>
+        <v>600</v>
       </c>
       <c r="AQ11" s="8" t="n">
         <v>0</v>
       </c>
       <c r="AR11" s="8" t="n">
-        <v>1.1</v>
+        <v>1100</v>
       </c>
       <c r="AS11" s="8" t="n">
-        <v>1.433</v>
+        <v>1433</v>
       </c>
       <c r="AT11" s="8" t="n">
-        <v>3.7</v>
+        <v>3700</v>
       </c>
       <c r="AU11" s="8" t="n">
-        <v>4.55</v>
+        <v>4550</v>
       </c>
     </row>
     <row r="12">
@@ -5700,142 +5589,142 @@
         </is>
       </c>
       <c r="B12" s="10" t="n">
-        <v>0.155</v>
+        <v>155</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>0.098</v>
+        <v>98</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.329</v>
+        <v>329</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>0.17</v>
+        <v>170</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>0.171</v>
+        <v>171</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>0.146</v>
+        <v>146</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>0.26</v>
+        <v>260</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>0.278</v>
+        <v>278</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.217</v>
+        <v>217</v>
       </c>
       <c r="K12" s="10" t="n">
-        <v>0.243</v>
+        <v>243</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>0.471</v>
+        <v>471</v>
       </c>
       <c r="M12" s="10" t="n">
-        <v>0.489</v>
+        <v>489</v>
       </c>
       <c r="N12" s="10" t="n">
-        <v>0.453</v>
+        <v>453</v>
       </c>
       <c r="O12" s="10" t="n">
-        <v>0.462</v>
+        <v>462</v>
       </c>
       <c r="P12" s="10" t="n">
-        <v>0.426</v>
+        <v>426</v>
       </c>
       <c r="Q12" s="10" t="n">
-        <v>0.674</v>
+        <v>674</v>
       </c>
       <c r="R12" s="10" t="n">
-        <v>0.86</v>
+        <v>860</v>
       </c>
       <c r="S12" s="10" t="n">
-        <v>0.55</v>
+        <v>550</v>
       </c>
       <c r="T12" s="10" t="n">
-        <v>1.006</v>
+        <v>1006</v>
       </c>
       <c r="U12" s="10" t="n">
-        <v>0.546</v>
+        <v>546</v>
       </c>
       <c r="V12" s="10" t="n">
-        <v>0.704</v>
+        <v>704</v>
       </c>
       <c r="W12" s="10" t="n">
-        <v>0.741</v>
+        <v>741</v>
       </c>
       <c r="X12" s="10" t="n">
-        <v>1.134</v>
+        <v>1134</v>
       </c>
       <c r="Y12" s="10" t="n">
-        <v>1.005</v>
+        <v>1005</v>
       </c>
       <c r="Z12" s="10" t="n">
-        <v>0.711</v>
+        <v>711</v>
       </c>
       <c r="AA12" s="10" t="n">
-        <v>1.827</v>
+        <v>1827</v>
       </c>
       <c r="AB12" s="10" t="n">
-        <v>1.479</v>
+        <v>1479</v>
       </c>
       <c r="AC12" s="10" t="n">
-        <v>1.14</v>
+        <v>1140</v>
       </c>
       <c r="AD12" s="10" t="n">
-        <v>2.04</v>
+        <v>2040</v>
       </c>
       <c r="AE12" s="10" t="n">
-        <v>1.368</v>
+        <v>1368</v>
       </c>
       <c r="AF12" s="10" t="n">
-        <v>0.453</v>
+        <v>453</v>
       </c>
       <c r="AG12" s="10" t="n">
-        <v>0.904</v>
+        <v>904</v>
       </c>
       <c r="AH12" s="10" t="n">
-        <v>0.855</v>
+        <v>855</v>
       </c>
       <c r="AI12" s="10" t="n">
-        <v>1.381</v>
+        <v>1381</v>
       </c>
       <c r="AJ12" s="10" t="n">
-        <v>0.788</v>
+        <v>788</v>
       </c>
       <c r="AK12" s="10" t="n">
-        <v>0.738</v>
+        <v>738</v>
       </c>
       <c r="AL12" s="10" t="n">
-        <v>0.777</v>
+        <v>777</v>
       </c>
       <c r="AM12" s="10" t="n">
-        <v>2.039</v>
+        <v>2039</v>
       </c>
       <c r="AN12" s="10" t="n">
-        <v>1.444</v>
+        <v>1444</v>
       </c>
       <c r="AO12" s="10" t="n">
-        <v>0.998</v>
+        <v>998</v>
       </c>
       <c r="AP12" s="10" t="n">
-        <v>1.898</v>
+        <v>1898</v>
       </c>
       <c r="AQ12" s="10" t="n">
-        <v>0.948</v>
+        <v>948</v>
       </c>
       <c r="AR12" s="10" t="n">
-        <v>2.738</v>
+        <v>2738</v>
       </c>
       <c r="AS12" s="10" t="n">
-        <v>2.593</v>
+        <v>2593</v>
       </c>
       <c r="AT12" s="10" t="n">
-        <v>6.278</v>
+        <v>6278</v>
       </c>
       <c r="AU12" s="10" t="n">
-        <v>6.313</v>
+        <v>6313</v>
       </c>
     </row>
   </sheetData>
@@ -5855,8 +5744,8 @@
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -5892,12 +5781,12 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>AI % of UK VC</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
           <t>Europe VC ($B)</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>AI % of UK VC</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -5910,19 +5799,19 @@
       <c r="A5" t="n">
         <v>2015</v>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="11" t="n">
         <v>7.5</v>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="11" t="n">
         <v>0.75</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" s="11" t="n">
         <v>20.71</v>
       </c>
-      <c r="E5" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="12" t="n">
         <v>36.2</v>
       </c>
     </row>
@@ -5930,19 +5819,19 @@
       <c r="A6" t="n">
         <v>2016</v>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="11" t="n">
         <v>9.35</v>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C6" s="11" t="n">
         <v>0.86</v>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E6" s="11" t="n">
         <v>24.09</v>
       </c>
-      <c r="E6" s="11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="12" t="n">
         <v>38.8</v>
       </c>
     </row>
@@ -5950,19 +5839,19 @@
       <c r="A7" t="n">
         <v>2017</v>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="11" t="n">
         <v>10.72</v>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="11" t="n">
         <v>1.42</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="12" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E7" s="11" t="n">
         <v>26.82</v>
       </c>
-      <c r="E7" s="11" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="12" t="n">
         <v>40</v>
       </c>
     </row>
@@ -5970,19 +5859,19 @@
       <c r="A8" t="n">
         <v>2018</v>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="11" t="n">
         <v>11.62</v>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C8" s="11" t="n">
         <v>2.01</v>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="12" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="E8" s="11" t="n">
         <v>33.51</v>
       </c>
-      <c r="E8" s="11" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="12" t="n">
         <v>34.7</v>
       </c>
     </row>
@@ -5990,19 +5879,19 @@
       <c r="A9" t="n">
         <v>2019</v>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="11" t="n">
         <v>17.65</v>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="11" t="n">
         <v>2.96</v>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="12" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="E9" s="11" t="n">
         <v>46.83</v>
       </c>
-      <c r="E9" s="11" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="12" t="n">
         <v>37.7</v>
       </c>
     </row>
@@ -6010,19 +5899,19 @@
       <c r="A10" t="n">
         <v>2020</v>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B10" s="11" t="n">
         <v>17.46</v>
       </c>
-      <c r="C10" s="8" t="n">
+      <c r="C10" s="11" t="n">
         <v>3.58</v>
       </c>
-      <c r="D10" s="8" t="n">
+      <c r="D10" s="12" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="E10" s="11" t="n">
         <v>48.03</v>
       </c>
-      <c r="E10" s="11" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="12" t="n">
         <v>36.4</v>
       </c>
     </row>
@@ -6030,19 +5919,19 @@
       <c r="A11" t="n">
         <v>2021</v>
       </c>
-      <c r="B11" s="8" t="n">
+      <c r="B11" s="11" t="n">
         <v>39.89</v>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C11" s="11" t="n">
         <v>5.16</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="12" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="E11" s="11" t="n">
         <v>118.19</v>
       </c>
-      <c r="E11" s="11" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="12" t="n">
         <v>33.8</v>
       </c>
     </row>
@@ -6050,19 +5939,19 @@
       <c r="A12" t="n">
         <v>2022</v>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B12" s="11" t="n">
         <v>30.77</v>
       </c>
-      <c r="C12" s="8" t="n">
+      <c r="C12" s="11" t="n">
         <v>4.76</v>
       </c>
-      <c r="D12" s="8" t="n">
+      <c r="D12" s="12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="E12" s="11" t="n">
         <v>94.97</v>
       </c>
-      <c r="E12" s="11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="12" t="n">
         <v>32.4</v>
       </c>
     </row>
@@ -6070,19 +5959,19 @@
       <c r="A13" t="n">
         <v>2023</v>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B13" s="11" t="n">
         <v>19.35</v>
       </c>
-      <c r="C13" s="8" t="n">
+      <c r="C13" s="11" t="n">
         <v>3.76</v>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D13" s="12" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="E13" s="11" t="n">
         <v>59.32</v>
       </c>
-      <c r="E13" s="11" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F13" s="11" t="n">
+      <c r="F13" s="12" t="n">
         <v>32.6</v>
       </c>
     </row>
@@ -6090,19 +5979,19 @@
       <c r="A14" t="n">
         <v>2024</v>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B14" s="11" t="n">
         <v>18.57</v>
       </c>
-      <c r="C14" s="8" t="n">
+      <c r="C14" s="11" t="n">
         <v>5.26</v>
       </c>
-      <c r="D14" s="8" t="n">
+      <c r="D14" s="12" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="E14" s="11" t="n">
         <v>56.08</v>
       </c>
-      <c r="E14" s="11" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="F14" s="11" t="n">
+      <c r="F14" s="12" t="n">
         <v>33.1</v>
       </c>
     </row>
@@ -6110,19 +5999,19 @@
       <c r="A15" t="n">
         <v>2025</v>
       </c>
-      <c r="B15" s="8" t="n">
+      <c r="B15" s="11" t="n">
         <v>23.66</v>
       </c>
-      <c r="C15" s="8" t="n">
+      <c r="C15" s="11" t="n">
         <v>8.18</v>
       </c>
-      <c r="D15" s="8" t="n">
+      <c r="D15" s="12" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="E15" s="11" t="n">
         <v>63.77</v>
       </c>
-      <c r="E15" s="11" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="12" t="n">
         <v>37.1</v>
       </c>
     </row>
@@ -6130,19 +6019,19 @@
       <c r="A16" t="n">
         <v>2026</v>
       </c>
-      <c r="B16" s="8" t="n">
+      <c r="B16" s="11" t="n">
         <v>17.06</v>
       </c>
-      <c r="C16" s="8" t="n">
+      <c r="C16" s="11" t="n">
         <v>12.59</v>
       </c>
-      <c r="D16" s="8" t="n">
+      <c r="D16" s="12" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="E16" s="11" t="n">
         <v>43.16</v>
       </c>
-      <c r="E16" s="11" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="F16" s="11" t="n">
+      <c r="F16" s="12" t="n">
         <v>39.5</v>
       </c>
     </row>
@@ -6205,7 +6094,7 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n">
+      <c r="C5" s="8" t="n">
         <v>2155</v>
       </c>
     </row>
@@ -6218,7 +6107,7 @@
           <t>China</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="8" t="n">
         <v>498</v>
       </c>
     </row>
@@ -6244,7 +6133,7 @@
           <t>Israel</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="8" t="n">
         <v>131</v>
       </c>
     </row>
@@ -6257,7 +6146,7 @@
           <t>India</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="8" t="n">
         <v>128</v>
       </c>
     </row>
@@ -6270,7 +6159,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="8" t="n">
         <v>92</v>
       </c>
     </row>
@@ -6283,7 +6172,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="8" t="n">
         <v>86</v>
       </c>
     </row>
@@ -6296,7 +6185,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="8" t="n">
         <v>66</v>
       </c>
     </row>
@@ -6322,7 +6211,7 @@
           <t>Sweden</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="C14" s="8" t="n">
         <v>57</v>
       </c>
     </row>
@@ -6335,7 +6224,7 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="C15" s="8" t="n">
         <v>48</v>
       </c>
     </row>
@@ -6411,7 +6300,7 @@
           <t>Cambridge</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="8" t="n">
         <v>15</v>
       </c>
     </row>
@@ -6424,7 +6313,7 @@
           <t>Manchester</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="8" t="n">
         <v>9</v>
       </c>
     </row>
@@ -6437,7 +6326,7 @@
           <t>Oxford</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="8" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6450,7 +6339,7 @@
           <t>Nottingham</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6463,7 +6352,7 @@
           <t>Birmingham</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6476,7 +6365,7 @@
           <t>Bristol</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6489,7 +6378,7 @@
           <t>Sheffield</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6502,7 +6391,7 @@
           <t>Leeds–Bradford</t>
         </is>
       </c>
-      <c r="C13" s="12" t="n">
+      <c r="C13" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6515,7 +6404,7 @@
           <t>Edinburgh</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="C14" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6528,7 +6417,7 @@
           <t>Windsor-Maidenhead</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="C15" s="8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6541,7 +6430,7 @@
           <t>Newcastle upon Tyne</t>
         </is>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="C16" s="8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6554,7 +6443,7 @@
           <t>Glasgow</t>
         </is>
       </c>
-      <c r="C17" s="12" t="n">
+      <c r="C17" s="8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6567,7 +6456,7 @@
           <t>Cardiff-Newport</t>
         </is>
       </c>
-      <c r="C18" s="12" t="n">
+      <c r="C18" s="8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6586,19 +6475,19 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6611,7 +6500,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Top metro areas by total VC raised, $B per year.</t>
+          <t>Top metro areas by total VC raised, $m per year.</t>
         </is>
       </c>
     </row>
@@ -6670,43 +6559,43 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>0</v>
+        <v>4865</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>0</v>
+        <v>6207</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>0</v>
+        <v>7167</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>0</v>
+        <v>7004</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>0</v>
+        <v>13424</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>0</v>
+        <v>12386</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0</v>
+        <v>28465</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0</v>
+        <v>22082</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>0</v>
+        <v>12237</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>0</v>
+        <v>12170</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0</v>
+        <v>17656</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>0</v>
+        <v>13630</v>
       </c>
       <c r="N5" s="10" t="n">
-        <v>157.29</v>
+        <v>157292</v>
       </c>
     </row>
     <row r="6">
@@ -6716,43 +6605,43 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>0</v>
+        <v>542</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>0</v>
+        <v>410</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>0</v>
+        <v>874</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0</v>
+        <v>772</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>0</v>
+        <v>506</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>0</v>
+        <v>2184</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0</v>
+        <v>883</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>0</v>
+        <v>1268</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>0</v>
+        <v>1860</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>0</v>
+        <v>2234</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>0</v>
+        <v>1241</v>
       </c>
       <c r="N6" s="10" t="n">
-        <v>13</v>
+        <v>12998</v>
       </c>
     </row>
     <row r="7">
@@ -6762,43 +6651,43 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0</v>
+        <v>651</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>0</v>
+        <v>358</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>0</v>
+        <v>339</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>0</v>
+        <v>736</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0</v>
+        <v>365</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>0</v>
+        <v>1070</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>0</v>
+        <v>2124</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0</v>
+        <v>1204</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>0</v>
+        <v>714</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>0</v>
+        <v>781</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>0</v>
+        <v>619</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="N7" s="10" t="n">
-        <v>9.199999999999999</v>
+        <v>9202</v>
       </c>
     </row>
     <row r="8">
@@ -6808,43 +6697,43 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>0</v>
+        <v>446</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>0</v>
+        <v>926</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>0</v>
+        <v>646</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>0</v>
+        <v>370</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>0</v>
+        <v>415</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="N8" s="10" t="n">
-        <v>4.25</v>
+        <v>4246</v>
       </c>
     </row>
     <row r="9">
@@ -6854,43 +6743,43 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0</v>
+        <v>549</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>0</v>
+        <v>441</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0</v>
+        <v>343</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>0</v>
+        <v>417</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="N9" s="10" t="n">
-        <v>2.94</v>
+        <v>2939</v>
       </c>
     </row>
     <row r="10">
@@ -6900,43 +6789,43 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0</v>
+        <v>262</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="N10" s="10" t="n">
-        <v>2.27</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="11">
@@ -6946,43 +6835,43 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>0</v>
+        <v>487</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>0</v>
+        <v>304</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>0</v>
+        <v>379</v>
       </c>
       <c r="N11" s="10" t="n">
-        <v>1.52</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="12">
@@ -6992,43 +6881,43 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>0</v>
+        <v>259</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N12" s="10" t="n">
-        <v>1.31</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="13">
@@ -7038,43 +6927,43 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>0</v>
+        <v>443</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="L13" s="8" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="N13" s="10" t="n">
-        <v>1.3</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="14">
@@ -7084,43 +6973,43 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="N14" s="10" t="n">
-        <v>1.17</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="15">
@@ -7130,43 +7019,43 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N15" s="10" t="n">
-        <v>0.86</v>
+        <v>864</v>
       </c>
     </row>
     <row r="16">
@@ -7176,43 +7065,43 @@
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="N16" s="10" t="n">
-        <v>0.86</v>
+        <v>860</v>
       </c>
     </row>
   </sheetData>
